--- a/ARG_WB_timeseries.xlsx
+++ b/ARG_WB_timeseries.xlsx
@@ -14,21 +14,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank liquid reserves to bank assets (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
+  <si>
+    <t>External debt stocks (% of GNI)</t>
+  </si>
+  <si>
+    <t>External debt stocks (current US$)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +482,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,418 +504,2650 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:37">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="E2">
+        <v>-0.172407656908035</v>
+      </c>
+      <c r="F2">
+        <v>-3.15992237703676</v>
+      </c>
+      <c r="G2">
+        <v>23.8947336198062</v>
+      </c>
+      <c r="H2">
+        <v>10.9863752325576</v>
+      </c>
+      <c r="I2">
+        <v>54.2417099417586</v>
+      </c>
+      <c r="J2">
+        <v>150062928187.3</v>
+      </c>
+      <c r="K2">
         <v>-0.78899893905691</v>
       </c>
-      <c r="D2">
+      <c r="L2">
+        <v>11499.9828002518</v>
+      </c>
+      <c r="M2">
+        <v>7637.01489203628</v>
+      </c>
+      <c r="N2">
+        <v>-1.90684139222867</v>
+      </c>
+      <c r="O2">
+        <v>51</v>
+      </c>
+      <c r="P2">
+        <v>-0.0280386935919523</v>
+      </c>
+      <c r="Q2">
+        <v>13.7841913064131</v>
+      </c>
+      <c r="R2">
+        <v>16.8328883767368</v>
+      </c>
+      <c r="S2">
+        <v>14.1776102532074</v>
+      </c>
+      <c r="T2">
+        <v>11.6360695451767</v>
+      </c>
+      <c r="V2">
         <v>20.1040140301883</v>
       </c>
-      <c r="E2">
+      <c r="W2">
+        <v>73.91</v>
+      </c>
+      <c r="X2">
+        <v>1.14882267666887</v>
+      </c>
+      <c r="Y2">
+        <v>-2.77220128165093</v>
+      </c>
+      <c r="Z2">
+        <v>0.0958238765597343</v>
+      </c>
+      <c r="AA2">
+        <v>37213984</v>
+      </c>
+      <c r="AB2">
+        <v>7.3</v>
+      </c>
+      <c r="AC2">
+        <v>0.182292386889458</v>
+      </c>
+      <c r="AD2">
+        <v>-0.214404493570328</v>
+      </c>
+      <c r="AE2">
         <v>9.622603501889049</v>
       </c>
-      <c r="F2">
+      <c r="AF2">
+        <v>25152117244.4134</v>
+      </c>
+      <c r="AG2">
+        <v>6.28322204626375</v>
+      </c>
+      <c r="AH2">
+        <v>22.6224447777343</v>
+      </c>
+      <c r="AI2">
         <v>15</v>
       </c>
+      <c r="AJ2">
+        <v>89.142</v>
+      </c>
+      <c r="AK2">
+        <v>0.418346971273422</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:37">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="F3">
+        <v>-1.40694788500181</v>
+      </c>
+      <c r="G3">
+        <v>20.833574652466</v>
+      </c>
+      <c r="H3">
+        <v>11.5790080825317</v>
+      </c>
+      <c r="I3">
+        <v>58.4932935172091</v>
+      </c>
+      <c r="J3">
+        <v>152649929432.5</v>
+      </c>
+      <c r="K3">
         <v>-4.40883968258557</v>
       </c>
-      <c r="D3">
+      <c r="L3">
+        <v>11117.754923787</v>
+      </c>
+      <c r="M3">
+        <v>7141.47507662826</v>
+      </c>
+      <c r="N3">
+        <v>-5.45263903304014</v>
+      </c>
+      <c r="O3">
+        <v>53.3</v>
+      </c>
+      <c r="Q3">
+        <v>14.1562743129569</v>
+      </c>
+      <c r="R3">
+        <v>16.9923529034125</v>
+      </c>
+      <c r="S3">
+        <v>13.7775019608536</v>
+      </c>
+      <c r="T3">
+        <v>10.2732473690136</v>
+      </c>
+      <c r="V3">
         <v>22.2743490173661</v>
       </c>
-      <c r="E3">
+      <c r="W3">
+        <v>74.154</v>
+      </c>
+      <c r="X3">
+        <v>1.18423354187058</v>
+      </c>
+      <c r="Y3">
+        <v>-3.31954145332982</v>
+      </c>
+      <c r="AA3">
+        <v>37624825</v>
+      </c>
+      <c r="AB3">
+        <v>10.7</v>
+      </c>
+      <c r="AE3">
         <v>9.324898793900561</v>
       </c>
-      <c r="F3">
+      <c r="AF3">
+        <v>14555552759.6102</v>
+      </c>
+      <c r="AG3">
+        <v>4.29371406025342</v>
+      </c>
+      <c r="AH3">
+        <v>21.8522554515453</v>
+      </c>
+      <c r="AI3">
         <v>17.32</v>
       </c>
+      <c r="AJ3">
+        <v>89.32899999999999</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:37">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="E4">
+        <v>-0.417055726051331</v>
+      </c>
+      <c r="F4">
+        <v>8.97078467784247</v>
+      </c>
+      <c r="G4">
+        <v>15.3318584042485</v>
+      </c>
+      <c r="H4">
+        <v>28.3825969991682</v>
+      </c>
+      <c r="I4">
+        <v>159.890183546743</v>
+      </c>
+      <c r="J4">
+        <v>148320192549.3</v>
+      </c>
+      <c r="K4">
         <v>-10.8944848285903</v>
       </c>
-      <c r="D4">
+      <c r="L4">
+        <v>9953.464928808569</v>
+      </c>
+      <c r="M4">
+        <v>2569.69963519124</v>
+      </c>
+      <c r="N4">
+        <v>-11.8423138177008</v>
+      </c>
+      <c r="O4">
+        <v>53.8</v>
+      </c>
+      <c r="P4">
+        <v>-0.228479072451591</v>
+      </c>
+      <c r="Q4">
+        <v>12.235247296692</v>
+      </c>
+      <c r="R4">
+        <v>19.6771706443151</v>
+      </c>
+      <c r="S4">
+        <v>14.0561136349095</v>
+      </c>
+      <c r="T4">
+        <v>13.370127359396</v>
+      </c>
+      <c r="V4">
         <v>34.2849338854665</v>
       </c>
-      <c r="E4">
+      <c r="W4">
+        <v>74.312</v>
+      </c>
+      <c r="X4">
+        <v>1.09188047859748</v>
+      </c>
+      <c r="Y4">
+        <v>-5.70628319150298</v>
+      </c>
+      <c r="Z4">
+        <v>-0.776545405387878</v>
+      </c>
+      <c r="AA4">
+        <v>38029349</v>
+      </c>
+      <c r="AB4">
+        <v>17.1</v>
+      </c>
+      <c r="AC4">
+        <v>-0.8807165622711181</v>
+      </c>
+      <c r="AD4">
+        <v>-0.761098086833954</v>
+      </c>
+      <c r="AE4">
         <v>9.81895834666325</v>
       </c>
-      <c r="F4">
+      <c r="AF4">
+        <v>10492424818.7375</v>
+      </c>
+      <c r="AG4">
+        <v>5.27543170673442</v>
+      </c>
+      <c r="AH4">
+        <v>41.7527243585642</v>
+      </c>
+      <c r="AI4">
         <v>19.59</v>
       </c>
+      <c r="AJ4">
+        <v>89.51000000000001</v>
+      </c>
+      <c r="AK4">
+        <v>0.260062754154205</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:37">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="E5">
+        <v>-0.479976803064346</v>
+      </c>
+      <c r="F5">
+        <v>6.37990680177011</v>
+      </c>
+      <c r="G5">
+        <v>10.7627059172487</v>
+      </c>
+      <c r="H5">
+        <v>25.9309429264224</v>
+      </c>
+      <c r="I5">
+        <v>133.474955613907</v>
+      </c>
+      <c r="J5">
+        <v>163442688409.3</v>
+      </c>
+      <c r="K5">
         <v>8.837040795769241</v>
       </c>
-      <c r="D5">
+      <c r="L5">
+        <v>10933.3925491594</v>
+      </c>
+      <c r="M5">
+        <v>3320.47775133903</v>
+      </c>
+      <c r="N5">
+        <v>7.71839038006088</v>
+      </c>
+      <c r="O5">
+        <v>51</v>
+      </c>
+      <c r="P5">
+        <v>-0.0342199839651585</v>
+      </c>
+      <c r="Q5">
+        <v>11.4380567929249</v>
+      </c>
+      <c r="R5">
+        <v>19.8373029880995</v>
+      </c>
+      <c r="S5">
+        <v>17.1997019513553</v>
+      </c>
+      <c r="T5">
+        <v>14.7138051046861</v>
+      </c>
+      <c r="V5">
         <v>30.0083948621788</v>
       </c>
-      <c r="E5">
+      <c r="W5">
+        <v>74.307</v>
+      </c>
+      <c r="X5">
+        <v>1.06089505704838</v>
+      </c>
+      <c r="Y5">
+        <v>-2.82936804297577</v>
+      </c>
+      <c r="Z5">
+        <v>-0.359838128089905</v>
+      </c>
+      <c r="AA5">
+        <v>38424282</v>
+      </c>
+      <c r="AB5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC5">
+        <v>-0.691475629806519</v>
+      </c>
+      <c r="AD5">
+        <v>-0.777115821838379</v>
+      </c>
+      <c r="AE5">
         <v>12.5187797002949</v>
       </c>
-      <c r="F5">
+      <c r="AF5">
+        <v>14157284136.3645</v>
+      </c>
+      <c r="AG5">
+        <v>5.70013745215417</v>
+      </c>
+      <c r="AH5">
+        <v>40.6447480311085</v>
+      </c>
+      <c r="AI5">
         <v>15.36</v>
       </c>
+      <c r="AJ5">
+        <v>89.68600000000001</v>
+      </c>
+      <c r="AK5">
+        <v>0.349125266075134</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:37">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="E6">
+        <v>-0.414409548044205</v>
+      </c>
+      <c r="F6">
+        <v>1.95058324319273</v>
+      </c>
+      <c r="G6">
+        <v>9.68251819633223</v>
+      </c>
+      <c r="H6">
+        <v>23.8476194239892</v>
+      </c>
+      <c r="I6">
+        <v>114.783966038451</v>
+      </c>
+      <c r="J6">
+        <v>167999635827.3</v>
+      </c>
+      <c r="K6">
         <v>9.02957330068152</v>
       </c>
-      <c r="D6">
+      <c r="L6">
+        <v>12117.6797423098</v>
+      </c>
+      <c r="M6">
+        <v>4242.02099089422</v>
+      </c>
+      <c r="N6">
+        <v>7.92951713016532</v>
+      </c>
+      <c r="O6">
+        <v>48.5</v>
+      </c>
+      <c r="P6">
+        <v>0.015197392553091</v>
+      </c>
+      <c r="Q6">
+        <v>11.114636067696</v>
+      </c>
+      <c r="R6">
+        <v>16.8763416365527</v>
+      </c>
+      <c r="S6">
+        <v>16.7347777696665</v>
+      </c>
+      <c r="T6">
+        <v>16.8450266849578</v>
+      </c>
+      <c r="V6">
         <v>26.3142537893684</v>
       </c>
-      <c r="E6">
+      <c r="W6">
+        <v>74.871</v>
+      </c>
+      <c r="X6">
+        <v>0.8832953588335291</v>
+      </c>
+      <c r="Y6">
+        <v>-0.425276316786125</v>
+      </c>
+      <c r="Z6">
+        <v>-0.610934913158417</v>
+      </c>
+      <c r="AA6">
+        <v>38815916</v>
+      </c>
+      <c r="AB6">
+        <v>6</v>
+      </c>
+      <c r="AC6">
+        <v>-0.698035299777985</v>
+      </c>
+      <c r="AD6">
+        <v>-0.767380177974701</v>
+      </c>
+      <c r="AE6">
         <v>13.1007798994386</v>
       </c>
-      <c r="F6">
+      <c r="AF6">
+        <v>19659591803.9788</v>
+      </c>
+      <c r="AG6">
+        <v>5.77837779911896</v>
+      </c>
+      <c r="AH6">
+        <v>40.692646108947</v>
+      </c>
+      <c r="AI6">
         <v>13.522</v>
       </c>
+      <c r="AJ6">
+        <v>89.86</v>
+      </c>
+      <c r="AK6">
+        <v>0.362040877342224</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:37">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
+        <v>9.249772637241129</v>
+      </c>
+      <c r="D7">
+        <v>5.18084337444251</v>
+      </c>
+      <c r="E7">
+        <v>-0.377738356590271</v>
+      </c>
+      <c r="F7">
+        <v>2.65363142179073</v>
+      </c>
+      <c r="G7">
+        <v>10.6534929189359</v>
+      </c>
+      <c r="H7">
+        <v>23.2458767338576</v>
+      </c>
+      <c r="I7">
+        <v>74.2469415660219</v>
+      </c>
+      <c r="J7">
+        <v>130788488210.2</v>
+      </c>
+      <c r="K7">
         <v>8.85165992013437</v>
       </c>
-      <c r="E7">
+      <c r="L7">
+        <v>13464.8128470561</v>
+      </c>
+      <c r="M7">
+        <v>5067.65342293276</v>
+      </c>
+      <c r="N7">
+        <v>7.73898107569444</v>
+      </c>
+      <c r="O7">
+        <v>47.8</v>
+      </c>
+      <c r="P7">
+        <v>-0.0979790613055229</v>
+      </c>
+      <c r="Q7">
+        <v>12.1418612359575</v>
+      </c>
+      <c r="S7">
+        <v>16.6216575161027</v>
+      </c>
+      <c r="T7">
+        <v>17.3053942367662</v>
+      </c>
+      <c r="W7">
+        <v>75.23099999999999</v>
+      </c>
+      <c r="X7">
+        <v>0.847154783885961</v>
+      </c>
+      <c r="Z7">
+        <v>-0.0417749434709549</v>
+      </c>
+      <c r="AA7">
+        <v>39216789</v>
+      </c>
+      <c r="AB7">
+        <v>4.4</v>
+      </c>
+      <c r="AC7">
+        <v>-0.525074362754822</v>
+      </c>
+      <c r="AD7">
+        <v>-0.557991087436676</v>
+      </c>
+      <c r="AE7">
         <v>13.1031756459852</v>
       </c>
-      <c r="F7">
+      <c r="AF7">
+        <v>28081718501.5579</v>
+      </c>
+      <c r="AG7">
+        <v>7.26029776298214</v>
+      </c>
+      <c r="AH7">
+        <v>40.5512709706238</v>
+      </c>
+      <c r="AI7">
         <v>11.506</v>
       </c>
+      <c r="AJ7">
+        <v>90.03100000000001</v>
+      </c>
+      <c r="AK7">
+        <v>0.269231617450714</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:37">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
+        <v>8.81033399559022</v>
+      </c>
+      <c r="D8">
+        <v>3.3907141955962</v>
+      </c>
+      <c r="E8">
+        <v>-0.33123853802681</v>
+      </c>
+      <c r="F8">
+        <v>2.79449564264943</v>
+      </c>
+      <c r="G8">
+        <v>11.9102616607561</v>
+      </c>
+      <c r="H8">
+        <v>23.0266946038115</v>
+      </c>
+      <c r="I8">
+        <v>52.8779757006235</v>
+      </c>
+      <c r="J8">
+        <v>118921233033.8</v>
+      </c>
+      <c r="K8">
         <v>8.047151500430269</v>
       </c>
-      <c r="E8">
+      <c r="L8">
+        <v>14843.5778659642</v>
+      </c>
+      <c r="M8">
+        <v>5869.38028970204</v>
+      </c>
+      <c r="N8">
+        <v>6.94185160089025</v>
+      </c>
+      <c r="O8">
+        <v>46.4</v>
+      </c>
+      <c r="P8">
+        <v>-0.0339163094758987</v>
+      </c>
+      <c r="Q8">
+        <v>12.4294153726307</v>
+      </c>
+      <c r="S8">
+        <v>17.2017551603052</v>
+      </c>
+      <c r="T8">
+        <v>17.4067852681036</v>
+      </c>
+      <c r="W8">
+        <v>75.279</v>
+      </c>
+      <c r="X8">
+        <v>0.788233877461469</v>
+      </c>
+      <c r="Z8">
+        <v>0.00196776282973588</v>
+      </c>
+      <c r="AA8">
+        <v>39622115</v>
+      </c>
+      <c r="AB8">
+        <v>3.5</v>
+      </c>
+      <c r="AC8">
+        <v>-0.61456698179245</v>
+      </c>
+      <c r="AD8">
+        <v>-0.57701563835144</v>
+      </c>
+      <c r="AE8">
         <v>12.8788866954319</v>
       </c>
-      <c r="F8">
+      <c r="AF8">
+        <v>32022297112.9806</v>
+      </c>
+      <c r="AG8">
+        <v>7.02897239370493</v>
+      </c>
+      <c r="AH8">
+        <v>40.4334798719151</v>
+      </c>
+      <c r="AI8">
         <v>10.078</v>
       </c>
+      <c r="AJ8">
+        <v>90.2</v>
+      </c>
+      <c r="AK8">
+        <v>0.403436541557312</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:37">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
+        <v>8.858356299746671</v>
+      </c>
+      <c r="D9">
+        <v>2.72684750122498</v>
+      </c>
+      <c r="E9">
+        <v>-0.372122079133987</v>
+      </c>
+      <c r="F9">
+        <v>2.1036160391819</v>
+      </c>
+      <c r="G9">
+        <v>13.0985413493544</v>
+      </c>
+      <c r="H9">
+        <v>22.6627503115066</v>
+      </c>
+      <c r="I9">
+        <v>43.1501917496034</v>
+      </c>
+      <c r="J9">
+        <v>120818039247.5</v>
+      </c>
+      <c r="K9">
         <v>9.00765087504757</v>
       </c>
-      <c r="E9">
+      <c r="L9">
+        <v>16455.1129801674</v>
+      </c>
+      <c r="M9">
+        <v>7185.25155147027</v>
+      </c>
+      <c r="N9">
+        <v>7.93261011269163</v>
+      </c>
+      <c r="O9">
+        <v>46.3</v>
+      </c>
+      <c r="P9">
+        <v>-0.0125325033441186</v>
+      </c>
+      <c r="Q9">
+        <v>12.9893238963619</v>
+      </c>
+      <c r="S9">
+        <v>17.9300729987004</v>
+      </c>
+      <c r="T9">
+        <v>18.2824203070644</v>
+      </c>
+      <c r="W9">
+        <v>74.783</v>
+      </c>
+      <c r="X9">
+        <v>0.792548175031362</v>
+      </c>
+      <c r="Z9">
+        <v>0.0977966338396072</v>
+      </c>
+      <c r="AA9">
+        <v>40016763</v>
+      </c>
+      <c r="AB9">
+        <v>2.8</v>
+      </c>
+      <c r="AC9">
+        <v>-0.6356935501098629</v>
+      </c>
+      <c r="AD9">
+        <v>-0.6014722585678099</v>
+      </c>
+      <c r="AE9">
         <v>12.4482684483004</v>
       </c>
-      <c r="F9">
+      <c r="AF9">
+        <v>46149456855.7802</v>
+      </c>
+      <c r="AG9">
+        <v>8.171534286186461</v>
+      </c>
+      <c r="AH9">
+        <v>40.945170618571</v>
+      </c>
+      <c r="AI9">
         <v>8.470000000000001</v>
       </c>
+      <c r="AJ9">
+        <v>90.366</v>
+      </c>
+      <c r="AK9">
+        <v>0.448621332645416</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:37">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>8.58269638340699</v>
+      </c>
+      <c r="D10">
+        <v>2.67920601141364</v>
+      </c>
+      <c r="E10">
+        <v>-0.434875011444092</v>
+      </c>
+      <c r="F10">
+        <v>1.49940141614234</v>
+      </c>
+      <c r="G10">
+        <v>12.313946714342</v>
+      </c>
+      <c r="H10">
+        <v>22.0609003826242</v>
+      </c>
+      <c r="I10">
+        <v>36.7970755463574</v>
+      </c>
+      <c r="J10">
+        <v>129752184881.3</v>
+      </c>
+      <c r="K10">
         <v>4.05723310346406</v>
       </c>
-      <c r="E10">
+      <c r="L10">
+        <v>17276.7570886806</v>
+      </c>
+      <c r="M10">
+        <v>8944.110265735701</v>
+      </c>
+      <c r="N10">
+        <v>3.00856892610517</v>
+      </c>
+      <c r="O10">
+        <v>45</v>
+      </c>
+      <c r="P10">
+        <v>-0.123509347438812</v>
+      </c>
+      <c r="Q10">
+        <v>13.6335132595631</v>
+      </c>
+      <c r="S10">
+        <v>18.9717341522181</v>
+      </c>
+      <c r="T10">
+        <v>18.341772996414</v>
+      </c>
+      <c r="W10">
+        <v>75.428</v>
+      </c>
+      <c r="X10">
+        <v>0.762756475390461</v>
+      </c>
+      <c r="Z10">
+        <v>-0.0877556875348091</v>
+      </c>
+      <c r="AA10">
+        <v>40424148</v>
+      </c>
+      <c r="AB10">
+        <v>2.6</v>
+      </c>
+      <c r="AC10">
+        <v>-0.702629446983337</v>
+      </c>
+      <c r="AD10">
+        <v>-0.699731647968292</v>
+      </c>
+      <c r="AE10">
         <v>13.3178463574032</v>
       </c>
-      <c r="F10">
+      <c r="AF10">
+        <v>46385380206.9801</v>
+      </c>
+      <c r="AG10">
+        <v>6.71425831138327</v>
+      </c>
+      <c r="AH10">
+        <v>40.4026733790382</v>
+      </c>
+      <c r="AI10">
         <v>7.837</v>
       </c>
+      <c r="AJ10">
+        <v>90.53</v>
+      </c>
+      <c r="AK10">
+        <v>0.358895927667618</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:37">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>8.54702664573378</v>
+      </c>
+      <c r="D11">
+        <v>2.98195821294241</v>
+      </c>
+      <c r="E11">
+        <v>-0.445475101470947</v>
+      </c>
+      <c r="F11">
+        <v>2.1785669619099</v>
+      </c>
+      <c r="G11">
+        <v>12.4162075416805</v>
+      </c>
+      <c r="H11">
+        <v>19.5609850560818</v>
+      </c>
+      <c r="I11">
+        <v>41.4244681423918</v>
+      </c>
+      <c r="J11">
+        <v>133695121247.7</v>
+      </c>
+      <c r="K11">
         <v>-5.91852507634947</v>
       </c>
-      <c r="E11">
+      <c r="L11">
+        <v>16182.0753477677</v>
+      </c>
+      <c r="M11">
+        <v>8150.23527028221</v>
+      </c>
+      <c r="N11">
+        <v>-6.9103121153056</v>
+      </c>
+      <c r="O11">
+        <v>43.8</v>
+      </c>
+      <c r="P11">
+        <v>-0.294032037258148</v>
+      </c>
+      <c r="Q11">
+        <v>15.903896746884</v>
+      </c>
+      <c r="S11">
+        <v>20.1360210279783</v>
+      </c>
+      <c r="T11">
+        <v>14.4961418494061</v>
+      </c>
+      <c r="W11">
+        <v>75.577</v>
+      </c>
+      <c r="X11">
+        <v>0.8865085766863851</v>
+      </c>
+      <c r="Z11">
+        <v>-0.234854578971863</v>
+      </c>
+      <c r="AA11">
+        <v>40854831</v>
+      </c>
+      <c r="AB11">
+        <v>2.4</v>
+      </c>
+      <c r="AC11">
+        <v>-0.8308367729187009</v>
+      </c>
+      <c r="AD11">
+        <v>-0.694468080997467</v>
+      </c>
+      <c r="AE11">
         <v>12.3830415594157</v>
       </c>
-      <c r="F11">
+      <c r="AF11">
+        <v>48006988635.3253</v>
+      </c>
+      <c r="AG11">
+        <v>9.067499928752429</v>
+      </c>
+      <c r="AH11">
+        <v>34.0571269054879</v>
+      </c>
+      <c r="AI11">
         <v>8.645</v>
       </c>
+      <c r="AJ11">
+        <v>90.691</v>
+      </c>
+      <c r="AK11">
+        <v>0.280091494321823</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:37">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>7.23503359658627</v>
+      </c>
+      <c r="C12">
+        <v>69.0114298006709</v>
+      </c>
+      <c r="D12">
+        <v>1.84399576317014</v>
+      </c>
+      <c r="E12">
+        <v>-0.355230033397675</v>
+      </c>
+      <c r="F12">
+        <v>-0.383118699737133</v>
+      </c>
+      <c r="G12">
+        <v>12.6901062454749</v>
+      </c>
+      <c r="H12">
+        <v>18.9338234053709</v>
+      </c>
+      <c r="I12">
+        <v>30.9493567310993</v>
+      </c>
+      <c r="J12">
+        <v>126642436908.2</v>
+      </c>
+      <c r="K12">
         <v>10.1253981561002</v>
       </c>
-      <c r="E12">
+      <c r="L12">
+        <v>17847.6110373178</v>
+      </c>
+      <c r="M12">
+        <v>10260.1313108254</v>
+      </c>
+      <c r="N12">
+        <v>8.968196728992821</v>
+      </c>
+      <c r="O12">
+        <v>43.7</v>
+      </c>
+      <c r="P12">
+        <v>-0.1117919459939</v>
+      </c>
+      <c r="Q12">
+        <v>15.1637178886417</v>
+      </c>
+      <c r="S12">
+        <v>21.2413164267537</v>
+      </c>
+      <c r="T12">
+        <v>16.0371898581987</v>
+      </c>
+      <c r="W12">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="X12">
+        <v>0.814878118220695</v>
+      </c>
+      <c r="Z12">
+        <v>-0.0847978666424751</v>
+      </c>
+      <c r="AA12">
+        <v>41288694</v>
+      </c>
+      <c r="AB12">
+        <v>1.5</v>
+      </c>
+      <c r="AC12">
+        <v>-0.742940902709961</v>
+      </c>
+      <c r="AD12">
+        <v>-0.59809422492981</v>
+      </c>
+      <c r="AE12">
         <v>12.8530426903255</v>
       </c>
-      <c r="F12">
+      <c r="AF12">
+        <v>52207549724.0928</v>
+      </c>
+      <c r="AG12">
+        <v>7.27697103967374</v>
+      </c>
+      <c r="AH12">
+        <v>34.9710132635696</v>
+      </c>
+      <c r="AI12">
         <v>7.714</v>
       </c>
+      <c r="AJ12">
+        <v>90.849</v>
+      </c>
+      <c r="AK12">
+        <v>0.361670136451721</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:37">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>6.86815902450533</v>
+      </c>
+      <c r="C13">
+        <v>49.6592791405416</v>
+      </c>
+      <c r="D13">
+        <v>1.22770795872113</v>
+      </c>
+      <c r="E13">
+        <v>-0.364098519086838</v>
+      </c>
+      <c r="F13">
+        <v>-1.00728084144866</v>
+      </c>
+      <c r="G13">
+        <v>14.0087151168124</v>
+      </c>
+      <c r="H13">
+        <v>18.4492091453155</v>
+      </c>
+      <c r="I13">
+        <v>27.7443463568229</v>
+      </c>
+      <c r="J13">
+        <v>142884643038.3</v>
+      </c>
+      <c r="K13">
         <v>6.00395169280579</v>
       </c>
-      <c r="E13">
+      <c r="L13">
+        <v>19104.9909405228</v>
+      </c>
+      <c r="M13">
+        <v>12704.2831819684</v>
+      </c>
+      <c r="N13">
+        <v>4.88127252804149</v>
+      </c>
+      <c r="O13">
+        <v>42.7</v>
+      </c>
+      <c r="P13">
+        <v>-0.07236106693744659</v>
+      </c>
+      <c r="Q13">
+        <v>15.6889565165983</v>
+      </c>
+      <c r="S13">
+        <v>20.196408074281</v>
+      </c>
+      <c r="T13">
+        <v>16.7569458546489</v>
+      </c>
+      <c r="W13">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="X13">
+        <v>0.764287095310235</v>
+      </c>
+      <c r="Z13">
+        <v>0.158993661403656</v>
+      </c>
+      <c r="AA13">
+        <v>41730660</v>
+      </c>
+      <c r="AB13">
+        <v>1.2</v>
+      </c>
+      <c r="AC13">
+        <v>-0.701964378356934</v>
+      </c>
+      <c r="AD13">
+        <v>-0.563123285770416</v>
+      </c>
+      <c r="AE13">
         <v>12.6636277012315</v>
       </c>
-      <c r="F13">
+      <c r="AF13">
+        <v>46265800525.8807</v>
+      </c>
+      <c r="AG13">
+        <v>5.20195157798821</v>
+      </c>
+      <c r="AH13">
+        <v>35.2061549999644</v>
+      </c>
+      <c r="AI13">
         <v>7.18</v>
       </c>
+      <c r="AJ13">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="AK13">
+        <v>0.344941824674606</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:37">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>7.2475325307913</v>
+      </c>
+      <c r="C14">
+        <v>49.1415989020508</v>
+      </c>
+      <c r="D14">
+        <v>1.53673589612636</v>
+      </c>
+      <c r="E14">
+        <v>-0.445909202098846</v>
+      </c>
+      <c r="F14">
+        <v>-0.39159512386959</v>
+      </c>
+      <c r="G14">
+        <v>15.2128150156924</v>
+      </c>
+      <c r="H14">
+        <v>16.2378594620246</v>
+      </c>
+      <c r="I14">
+        <v>26.2398392717053</v>
+      </c>
+      <c r="J14">
+        <v>139877658066.6</v>
+      </c>
+      <c r="K14">
         <v>-1.0264204544321</v>
       </c>
-      <c r="E14">
+      <c r="L14">
+        <v>19430.4178068112</v>
+      </c>
+      <c r="M14">
+        <v>12949.717486654</v>
+      </c>
+      <c r="N14">
+        <v>-2.0383253093713</v>
+      </c>
+      <c r="O14">
+        <v>41.4</v>
+      </c>
+      <c r="P14">
+        <v>-0.206967011094093</v>
+      </c>
+      <c r="Q14">
+        <v>16.6454378106252</v>
+      </c>
+      <c r="S14">
+        <v>21.182234604867</v>
+      </c>
+      <c r="T14">
+        <v>14.2886829096862</v>
+      </c>
+      <c r="W14">
+        <v>75.80200000000001</v>
+      </c>
+      <c r="X14">
+        <v>0.784824735364742</v>
+      </c>
+      <c r="Z14">
+        <v>0.103040546178818</v>
+      </c>
+      <c r="AA14">
+        <v>42161721</v>
+      </c>
+      <c r="AB14">
+        <v>1.3</v>
+      </c>
+      <c r="AC14">
+        <v>-0.897686779499054</v>
+      </c>
+      <c r="AD14">
+        <v>-0.623034238815308</v>
+      </c>
+      <c r="AE14">
         <v>12.9528415127413</v>
       </c>
-      <c r="F14">
+      <c r="AF14">
+        <v>43223270863.843</v>
+      </c>
+      <c r="AG14">
+        <v>5.21829041219894</v>
+      </c>
+      <c r="AH14">
+        <v>30.5265423717108</v>
+      </c>
+      <c r="AI14">
         <v>7.217</v>
       </c>
+      <c r="AJ14">
+        <v>91.121</v>
+      </c>
+      <c r="AK14">
+        <v>0.295209914445877</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:37">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>10.1560460352012</v>
+      </c>
+      <c r="C15">
+        <v>47.4397307032506</v>
+      </c>
+      <c r="D15">
+        <v>1.53372870982538</v>
+      </c>
+      <c r="E15">
+        <v>-0.434306710958481</v>
+      </c>
+      <c r="F15">
+        <v>-2.37749566620574</v>
+      </c>
+      <c r="G15">
+        <v>15.7290920133564</v>
+      </c>
+      <c r="H15">
+        <v>14.6171733884386</v>
+      </c>
+      <c r="I15">
+        <v>27.809883508059</v>
+      </c>
+      <c r="J15">
+        <v>150225027402.1</v>
+      </c>
+      <c r="K15">
         <v>2.40532378079436</v>
       </c>
-      <c r="E15">
+      <c r="L15">
+        <v>19928.989490167</v>
+      </c>
+      <c r="M15">
+        <v>12963.675773326</v>
+      </c>
+      <c r="N15">
+        <v>1.39351266056681</v>
+      </c>
+      <c r="O15">
+        <v>41.1</v>
+      </c>
+      <c r="P15">
+        <v>-0.254236966371536</v>
+      </c>
+      <c r="Q15">
+        <v>16.8062377968797</v>
+      </c>
+      <c r="S15">
+        <v>21.5652829643596</v>
+      </c>
+      <c r="T15">
+        <v>14.7167556136651</v>
+      </c>
+      <c r="W15">
+        <v>75.82899999999999</v>
+      </c>
+      <c r="X15">
+        <v>0.8377364272139201</v>
+      </c>
+      <c r="Z15">
+        <v>0.0653142631053925</v>
+      </c>
+      <c r="AA15">
+        <v>42582455</v>
+      </c>
+      <c r="AB15">
+        <v>1.1</v>
+      </c>
+      <c r="AC15">
+        <v>-0.928134799003601</v>
+      </c>
+      <c r="AD15">
+        <v>-0.656328618526459</v>
+      </c>
+      <c r="AE15">
         <v>12.4529027558077</v>
       </c>
-      <c r="F15">
+      <c r="AF15">
+        <v>30533919650.6264</v>
+      </c>
+      <c r="AG15">
+        <v>3.46015205462158</v>
+      </c>
+      <c r="AH15">
+        <v>29.3339290021037</v>
+      </c>
+      <c r="AI15">
         <v>7.1</v>
       </c>
+      <c r="AJ15">
+        <v>91.249</v>
+      </c>
+      <c r="AK15">
+        <v>0.276933550834656</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:37">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>9.99137338188928</v>
+      </c>
+      <c r="C16">
+        <v>59.9216117732519</v>
+      </c>
+      <c r="D16">
+        <v>1.79255873857878</v>
+      </c>
+      <c r="E16">
+        <v>-0.549791395664215</v>
+      </c>
+      <c r="F16">
+        <v>-1.74400211981355</v>
+      </c>
+      <c r="G16">
+        <v>13.8237692455151</v>
+      </c>
+      <c r="H16">
+        <v>14.4054785893756</v>
+      </c>
+      <c r="I16">
+        <v>30.3338678915012</v>
+      </c>
+      <c r="J16">
+        <v>156380868987.6</v>
+      </c>
+      <c r="K16">
         <v>-2.51261532081394</v>
       </c>
-      <c r="D16">
+      <c r="L16">
+        <v>19487.4181748868</v>
+      </c>
+      <c r="M16">
+        <v>12233.1444119186</v>
+      </c>
+      <c r="N16">
+        <v>-3.51326421042003</v>
+      </c>
+      <c r="O16">
+        <v>41.8</v>
+      </c>
+      <c r="P16">
+        <v>-0.111114293336868</v>
+      </c>
+      <c r="Q16">
+        <v>16.9498757371062</v>
+      </c>
+      <c r="R16">
+        <v>24.5697808575806</v>
+      </c>
+      <c r="S16">
+        <v>22.3322943705014</v>
+      </c>
+      <c r="T16">
+        <v>14.0013150558519</v>
+      </c>
+      <c r="V16">
         <v>7.75788916526639</v>
       </c>
-      <c r="E16">
+      <c r="W16">
+        <v>76.268</v>
+      </c>
+      <c r="X16">
+        <v>0.878100924236765</v>
+      </c>
+      <c r="Y16">
+        <v>-2.90614606577065</v>
+      </c>
+      <c r="Z16">
+        <v>-0.00512187136337161</v>
+      </c>
+      <c r="AA16">
+        <v>43024071</v>
+      </c>
+      <c r="AB16">
+        <v>1.1</v>
+      </c>
+      <c r="AC16">
+        <v>-1.0661495923996</v>
+      </c>
+      <c r="AD16">
+        <v>-0.866627335548401</v>
+      </c>
+      <c r="AE16">
         <v>12.6109666067191</v>
       </c>
-      <c r="F16">
+      <c r="AF16">
+        <v>31410813269.5239</v>
+      </c>
+      <c r="AG16">
+        <v>3.96299919336678</v>
+      </c>
+      <c r="AH16">
+        <v>28.4067936452275</v>
+      </c>
+      <c r="AI16">
         <v>7.268</v>
       </c>
+      <c r="AJ16">
+        <v>91.377</v>
+      </c>
+      <c r="AK16">
+        <v>0.34527176618576</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:37">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>9.435091347684329</v>
+      </c>
+      <c r="C17">
+        <v>61.3477780713524</v>
+      </c>
+      <c r="D17">
+        <v>1.57420132816491</v>
+      </c>
+      <c r="E17">
+        <v>-0.581265270709991</v>
+      </c>
+      <c r="F17">
+        <v>-2.96292666513534</v>
+      </c>
+      <c r="G17">
+        <v>14.4142330417064</v>
+      </c>
+      <c r="H17">
+        <v>10.7056520504538</v>
+      </c>
+      <c r="I17">
+        <v>32.2082949986265</v>
+      </c>
+      <c r="J17">
+        <v>187972586465.6</v>
+      </c>
+      <c r="K17">
         <v>2.73115982828944</v>
       </c>
-      <c r="D17">
+      <c r="L17">
+        <v>19899.1499275245</v>
+      </c>
+      <c r="M17">
+        <v>13679.6264980954</v>
+      </c>
+      <c r="N17">
+        <v>1.66091253843923</v>
+      </c>
+      <c r="P17">
+        <v>-0.0494756102561951</v>
+      </c>
+      <c r="Q17">
+        <v>18.098379759087</v>
+      </c>
+      <c r="R17">
+        <v>25.0083932347048</v>
+      </c>
+      <c r="S17">
+        <v>22.1490803040164</v>
+      </c>
+      <c r="T17">
+        <v>11.7805740385254</v>
+      </c>
+      <c r="V17">
         <v>7.37421073749561</v>
       </c>
-      <c r="E17">
+      <c r="W17">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="X17">
+        <v>0.850128597463815</v>
+      </c>
+      <c r="Y17">
+        <v>-3.39011034719535</v>
+      </c>
+      <c r="Z17">
+        <v>0.00876413471996784</v>
+      </c>
+      <c r="AA17">
+        <v>43477012</v>
+      </c>
+      <c r="AC17">
+        <v>-0.898022353649139</v>
+      </c>
+      <c r="AD17">
+        <v>-0.74863588809967</v>
+      </c>
+      <c r="AE17">
         <v>12.3365069418291</v>
       </c>
-      <c r="F17">
+      <c r="AF17">
+        <v>25520565580.4894</v>
+      </c>
+      <c r="AG17">
+        <v>3.36214425707702</v>
+      </c>
+      <c r="AH17">
+        <v>22.4862260889792</v>
+      </c>
+      <c r="AI17">
         <v>7.579</v>
       </c>
+      <c r="AJ17">
+        <v>91.503</v>
+      </c>
+      <c r="AK17">
+        <v>0.411758154630661</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:37">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>8.868712471689919</v>
+      </c>
+      <c r="C18">
+        <v>66.22886452080169</v>
+      </c>
+      <c r="D18">
+        <v>1.70027750562075</v>
+      </c>
+      <c r="E18">
+        <v>-0.299235552549362</v>
+      </c>
+      <c r="F18">
+        <v>-2.70922168361454</v>
+      </c>
+      <c r="G18">
+        <v>13.6676334273514</v>
+      </c>
+      <c r="H18">
+        <v>12.5270951690009</v>
+      </c>
+      <c r="I18">
+        <v>35.1613251074643</v>
+      </c>
+      <c r="J18">
+        <v>191717702190.7</v>
+      </c>
+      <c r="K18">
         <v>-2.08032784377811</v>
       </c>
-      <c r="D18">
+      <c r="L18">
+        <v>20105.761359796</v>
+      </c>
+      <c r="M18">
+        <v>12699.9623137756</v>
+      </c>
+      <c r="N18">
+        <v>-3.02450095578762</v>
+      </c>
+      <c r="O18">
+        <v>42.3</v>
+      </c>
+      <c r="P18">
+        <v>0.218796372413635</v>
+      </c>
+      <c r="Q18">
+        <v>17.6545781863509</v>
+      </c>
+      <c r="R18">
+        <v>26.1799164832469</v>
+      </c>
+      <c r="S18">
+        <v>21.2567013071388</v>
+      </c>
+      <c r="T18">
+        <v>13.5667926798789</v>
+      </c>
+      <c r="V18">
         <v>11.3900941602608</v>
       </c>
-      <c r="E18">
+      <c r="W18">
+        <v>76.105</v>
+      </c>
+      <c r="X18">
+        <v>0.809245362717563</v>
+      </c>
+      <c r="Y18">
+        <v>-5.33377782706346</v>
+      </c>
+      <c r="Z18">
+        <v>0.197749897837639</v>
+      </c>
+      <c r="AA18">
+        <v>43900313</v>
+      </c>
+      <c r="AB18">
+        <v>1.3</v>
+      </c>
+      <c r="AC18">
+        <v>-0.347571164369583</v>
+      </c>
+      <c r="AD18">
+        <v>-0.320159524679184</v>
+      </c>
+      <c r="AE18">
         <v>12.0972836411962</v>
       </c>
-      <c r="F18">
+      <c r="AF18">
+        <v>38414518491.6132</v>
+      </c>
+      <c r="AG18">
+        <v>5.09719624487539</v>
+      </c>
+      <c r="AH18">
+        <v>26.0938878488799</v>
+      </c>
+      <c r="AI18">
         <v>8.085000000000001</v>
       </c>
+      <c r="AJ18">
+        <v>91.627</v>
+      </c>
+      <c r="AK18">
+        <v>0.49326366186142</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:37">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>10.1924279555023</v>
+      </c>
+      <c r="C19">
+        <v>50.2817382851133</v>
+      </c>
+      <c r="D19">
+        <v>1.73479928371252</v>
+      </c>
+      <c r="E19">
+        <v>-0.309002459049225</v>
+      </c>
+      <c r="F19">
+        <v>-4.83995921807391</v>
+      </c>
+      <c r="G19">
+        <v>15.9584973420583</v>
+      </c>
+      <c r="H19">
+        <v>11.3202833596733</v>
+      </c>
+      <c r="I19">
+        <v>37.7365221801036</v>
+      </c>
+      <c r="J19">
+        <v>236683642186.1</v>
+      </c>
+      <c r="K19">
         <v>2.81850297775918</v>
       </c>
-      <c r="D19">
+      <c r="L19">
+        <v>23385.0740904917</v>
+      </c>
+      <c r="M19">
+        <v>14532.5009308511</v>
+      </c>
+      <c r="N19">
+        <v>1.91639608148853</v>
+      </c>
+      <c r="O19">
+        <v>41.4</v>
+      </c>
+      <c r="P19">
+        <v>0.135085612535477</v>
+      </c>
+      <c r="Q19">
+        <v>17.6968939223042</v>
+      </c>
+      <c r="R19">
+        <v>24.2825320419979</v>
+      </c>
+      <c r="S19">
+        <v>19.3371239744582</v>
+      </c>
+      <c r="T19">
+        <v>13.9693177780045</v>
+      </c>
+      <c r="V19">
         <v>9.419814018022439</v>
       </c>
-      <c r="E19">
+      <c r="W19">
+        <v>76.54300000000001</v>
+      </c>
+      <c r="X19">
+        <v>0.84775481125944</v>
+      </c>
+      <c r="Y19">
+        <v>-5.51824569508007</v>
+      </c>
+      <c r="Z19">
+        <v>0.162542164325714</v>
+      </c>
+      <c r="AA19">
+        <v>44288894</v>
+      </c>
+      <c r="AB19">
+        <v>1.1</v>
+      </c>
+      <c r="AC19">
+        <v>-0.196430206298828</v>
+      </c>
+      <c r="AD19">
+        <v>-0.237312033772469</v>
+      </c>
+      <c r="AE19">
         <v>10.939623860491</v>
       </c>
-      <c r="F19">
+      <c r="AF19">
+        <v>55314409205.2189</v>
+      </c>
+      <c r="AG19">
+        <v>6.05038766582561</v>
+      </c>
+      <c r="AH19">
+        <v>25.2896011376779</v>
+      </c>
+      <c r="AI19">
         <v>8.347</v>
       </c>
+      <c r="AJ19">
+        <v>91.749</v>
+      </c>
+      <c r="AK19">
+        <v>0.528708100318909</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:37">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>8.648660005150379</v>
+      </c>
+      <c r="C20">
+        <v>68.3339359683885</v>
+      </c>
+      <c r="D20">
+        <v>2.95778551361675</v>
+      </c>
+      <c r="E20">
+        <v>-0.0992739275097847</v>
+      </c>
+      <c r="F20">
+        <v>-5.16055257152295</v>
+      </c>
+      <c r="H20">
+        <v>14.4366857499034</v>
+      </c>
+      <c r="I20">
+        <v>58.6307152401281</v>
+      </c>
+      <c r="J20">
+        <v>296726558406.2</v>
+      </c>
+      <c r="K20">
         <v>-2.61739646282038</v>
       </c>
-      <c r="C20">
+      <c r="L20">
+        <v>24410.3919063335</v>
+      </c>
+      <c r="M20">
+        <v>11752.7998922979</v>
+      </c>
+      <c r="N20">
+        <v>-3.41553683867816</v>
+      </c>
+      <c r="O20">
+        <v>41.7</v>
+      </c>
+      <c r="P20">
+        <v>0.0280606187880039</v>
+      </c>
+      <c r="Q20">
+        <v>15.8050971558947</v>
+      </c>
+      <c r="R20">
+        <v>22.6709430512171</v>
+      </c>
+      <c r="S20">
+        <v>17.7024488717292</v>
+      </c>
+      <c r="T20">
+        <v>16.3258502050892</v>
+      </c>
+      <c r="U20">
         <v>34.2772237131003</v>
       </c>
-      <c r="D20">
+      <c r="V20">
         <v>12.8793045637226</v>
       </c>
-      <c r="E20">
+      <c r="W20">
+        <v>76.77</v>
+      </c>
+      <c r="X20">
+        <v>0.732300347538541</v>
+      </c>
+      <c r="Y20">
+        <v>-5.33635226717988</v>
+      </c>
+      <c r="Z20">
+        <v>0.00690981233492494</v>
+      </c>
+      <c r="AA20">
+        <v>44654882</v>
+      </c>
+      <c r="AB20">
+        <v>1.6</v>
+      </c>
+      <c r="AC20">
+        <v>-0.195977628231049</v>
+      </c>
+      <c r="AD20">
+        <v>-0.219330430030823</v>
+      </c>
+      <c r="AE20">
         <v>9.79144712037089</v>
       </c>
-      <c r="F20">
+      <c r="AF20">
+        <v>66221501691.4418</v>
+      </c>
+      <c r="AG20">
+        <v>7.11111211150086</v>
+      </c>
+      <c r="AH20">
+        <v>30.7625359549926</v>
+      </c>
+      <c r="AI20">
         <v>9.220000000000001</v>
       </c>
+      <c r="AJ20">
+        <v>91.87</v>
+      </c>
+      <c r="AK20">
+        <v>0.5392525792121891</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:37">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>9.72634066738099</v>
+      </c>
+      <c r="C21">
+        <v>71.1342740484745</v>
+      </c>
+      <c r="D21">
+        <v>5.7029147138395</v>
+      </c>
+      <c r="E21">
+        <v>-0.107116244733334</v>
+      </c>
+      <c r="F21">
+        <v>-0.779998447561848</v>
+      </c>
+      <c r="G21">
+        <v>14.4776292447323</v>
+      </c>
+      <c r="H21">
+        <v>17.9248783778462</v>
+      </c>
+      <c r="I21">
+        <v>69.5902998339522</v>
+      </c>
+      <c r="J21">
+        <v>299354360388</v>
+      </c>
+      <c r="K21">
         <v>-2.00086100285785</v>
       </c>
-      <c r="C21">
+      <c r="L21">
+        <v>23516.8261980886</v>
+      </c>
+      <c r="M21">
+        <v>9955.97478680428</v>
+      </c>
+      <c r="N21">
+        <v>-2.69506723533574</v>
+      </c>
+      <c r="O21">
+        <v>43.3</v>
+      </c>
+      <c r="P21">
+        <v>-0.120795331895351</v>
+      </c>
+      <c r="Q21">
+        <v>16.4432415862976</v>
+      </c>
+      <c r="R21">
+        <v>22.0364845686943</v>
+      </c>
+      <c r="S21">
+        <v>17.7888990504455</v>
+      </c>
+      <c r="T21">
+        <v>14.7057366680037</v>
+      </c>
+      <c r="U21">
         <v>53.5483043492339</v>
       </c>
-      <c r="D21">
+      <c r="V21">
         <v>15.7967986276777</v>
       </c>
-      <c r="E21">
+      <c r="W21">
+        <v>76.84699999999999</v>
+      </c>
+      <c r="X21">
+        <v>0.699696134379197</v>
+      </c>
+      <c r="Y21">
+        <v>-4.92889704924096</v>
+      </c>
+      <c r="Z21">
+        <v>-0.0978230908513069</v>
+      </c>
+      <c r="AA21">
+        <v>44973465</v>
+      </c>
+      <c r="AB21">
+        <v>1.7</v>
+      </c>
+      <c r="AC21">
+        <v>-0.453079700469971</v>
+      </c>
+      <c r="AD21">
+        <v>-0.427360445261002</v>
+      </c>
+      <c r="AE21">
         <v>10.3919973375121</v>
       </c>
-      <c r="F21">
+      <c r="AF21">
+        <v>44880566052.3703</v>
+      </c>
+      <c r="AG21">
+        <v>5.94220121846315</v>
+      </c>
+      <c r="AH21">
+        <v>32.6306150458499</v>
+      </c>
+      <c r="AI21">
         <v>9.843</v>
       </c>
+      <c r="AJ21">
+        <v>91.991</v>
+      </c>
+      <c r="AK21">
+        <v>0.570874631404877</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:37">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>12.4102181705815</v>
+      </c>
+      <c r="C22">
+        <v>100.440665352195</v>
+      </c>
+      <c r="D22">
+        <v>4.15006400338998</v>
+      </c>
+      <c r="E22">
+        <v>-0.163570061326027</v>
+      </c>
+      <c r="F22">
+        <v>0.6969353611360311</v>
+      </c>
+      <c r="G22">
+        <v>15.746489768328</v>
+      </c>
+      <c r="H22">
+        <v>16.6054144372484</v>
+      </c>
+      <c r="I22">
+        <v>73.39264455913541</v>
+      </c>
+      <c r="J22">
+        <v>275474929878.8</v>
+      </c>
+      <c r="K22">
         <v>-9.900484813646401</v>
       </c>
-      <c r="C22">
+      <c r="L22">
+        <v>22393.3479575353</v>
+      </c>
+      <c r="M22">
+        <v>8535.59938004389</v>
+      </c>
+      <c r="N22">
+        <v>-10.3361096878518</v>
+      </c>
+      <c r="O22">
+        <v>42.7</v>
+      </c>
+      <c r="P22">
+        <v>-0.254261821508408</v>
+      </c>
+      <c r="Q22">
+        <v>16.8730073837365</v>
+      </c>
+      <c r="R22">
+        <v>25.8405452538391</v>
+      </c>
+      <c r="S22">
+        <v>17.4777322783093</v>
+      </c>
+      <c r="T22">
+        <v>13.5982843701675</v>
+      </c>
+      <c r="U22">
         <v>42.0150947376509</v>
       </c>
-      <c r="D22">
+      <c r="V22">
         <v>7.50264305918987</v>
       </c>
-      <c r="E22">
+      <c r="W22">
+        <v>75.878</v>
+      </c>
+      <c r="X22">
+        <v>0.734111593948744</v>
+      </c>
+      <c r="Y22">
+        <v>-8.6954919523039</v>
+      </c>
+      <c r="Z22">
+        <v>-0.0719974040985107</v>
+      </c>
+      <c r="AA22">
+        <v>45191965</v>
+      </c>
+      <c r="AB22">
+        <v>2.2</v>
+      </c>
+      <c r="AC22">
+        <v>-0.498344272375107</v>
+      </c>
+      <c r="AD22">
+        <v>-0.486265957355499</v>
+      </c>
+      <c r="AE22">
         <v>10.70812114449</v>
       </c>
-      <c r="F22">
+      <c r="AF22">
+        <v>39403734630.1228</v>
+      </c>
+      <c r="AG22">
+        <v>7.09405401009515</v>
+      </c>
+      <c r="AH22">
+        <v>30.203698807416</v>
+      </c>
+      <c r="AI22">
         <v>11.461</v>
       </c>
+      <c r="AJ22">
+        <v>92.111</v>
+      </c>
+      <c r="AK22">
+        <v>0.584501206874847</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:37">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>12.983902466712</v>
+      </c>
+      <c r="C23">
+        <v>113.169644263274</v>
+      </c>
+      <c r="D23">
+        <v>4.29211290587395</v>
+      </c>
+      <c r="E23">
+        <v>-0.422596842050552</v>
+      </c>
+      <c r="F23">
+        <v>1.36154422203441</v>
+      </c>
+      <c r="G23">
+        <v>13.2644289814535</v>
+      </c>
+      <c r="H23">
+        <v>18.0667091690365</v>
+      </c>
+      <c r="I23">
+        <v>55.9476971135758</v>
+      </c>
+      <c r="J23">
+        <v>266759890414</v>
+      </c>
+      <c r="K23">
         <v>10.4418119882506</v>
       </c>
-      <c r="C23">
+      <c r="L23">
+        <v>26300.274261175</v>
+      </c>
+      <c r="M23">
+        <v>10738.0179223384</v>
+      </c>
+      <c r="N23">
+        <v>10.1485599877349</v>
+      </c>
+      <c r="O23">
+        <v>42.4</v>
+      </c>
+      <c r="P23">
+        <v>-0.390557259321213</v>
+      </c>
+      <c r="Q23">
+        <v>15.9158179423023</v>
+      </c>
+      <c r="R23">
+        <v>22.8967903877811</v>
+      </c>
+      <c r="S23">
+        <v>18.0764989044589</v>
+      </c>
+      <c r="T23">
+        <v>15.0119803984295</v>
+      </c>
+      <c r="U23">
         <v>48.4093786255199</v>
       </c>
-      <c r="D23">
+      <c r="V23">
         <v>6.52367466313931</v>
       </c>
-      <c r="E23">
+      <c r="W23">
+        <v>73.94799999999999</v>
+      </c>
+      <c r="X23">
+        <v>0.630055381810861</v>
+      </c>
+      <c r="Y23">
+        <v>-4.37239542495983</v>
+      </c>
+      <c r="Z23">
+        <v>0.000530058634467423</v>
+      </c>
+      <c r="AA23">
+        <v>45312281</v>
+      </c>
+      <c r="AB23">
+        <v>1.4</v>
+      </c>
+      <c r="AC23">
+        <v>-0.631172716617584</v>
+      </c>
+      <c r="AD23">
+        <v>-0.477947890758514</v>
+      </c>
+      <c r="AE23">
         <v>11.3410740330927</v>
       </c>
-      <c r="F23">
+      <c r="AF23">
+        <v>39653498610.7828</v>
+      </c>
+      <c r="AG23">
+        <v>5.6049034262494</v>
+      </c>
+      <c r="AH23">
+        <v>33.078689567466</v>
+      </c>
+      <c r="AI23">
         <v>8.736000000000001</v>
       </c>
+      <c r="AJ23">
+        <v>92.229</v>
+      </c>
+      <c r="AK23">
+        <v>0.610777020454407</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:37">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
+        <v>14.7351915493971</v>
+      </c>
+      <c r="C24">
+        <v>122.356829067892</v>
+      </c>
+      <c r="D24">
+        <v>3.09401335778846</v>
+      </c>
+      <c r="E24">
+        <v>-0.447221606969833</v>
+      </c>
+      <c r="F24">
+        <v>-0.626443919210919</v>
+      </c>
+      <c r="G24">
+        <v>12.9136184380619</v>
+      </c>
+      <c r="H24">
+        <v>16.248014443903</v>
+      </c>
+      <c r="I24">
+        <v>42.9676924073569</v>
+      </c>
+      <c r="J24">
+        <v>266900361822</v>
+      </c>
+      <c r="K24">
         <v>5.26987967384072</v>
       </c>
-      <c r="C24">
+      <c r="L24">
+        <v>29597.6938429263</v>
+      </c>
+      <c r="M24">
+        <v>13935.6811110049</v>
+      </c>
+      <c r="N24">
+        <v>5.04819532337936</v>
+      </c>
+      <c r="O24">
+        <v>40.7</v>
+      </c>
+      <c r="P24">
+        <v>-0.28348970413208</v>
+      </c>
+      <c r="Q24">
+        <v>15.8356571842994</v>
+      </c>
+      <c r="R24">
+        <v>21.9068187207194</v>
+      </c>
+      <c r="S24">
+        <v>17.9272315382489</v>
+      </c>
+      <c r="T24">
+        <v>15.2996935612041</v>
+      </c>
+      <c r="U24">
         <v>72.430757531824</v>
       </c>
-      <c r="D24">
+      <c r="V24">
         <v>7.76084028840006</v>
       </c>
-      <c r="E24">
+      <c r="W24">
+        <v>75.806</v>
+      </c>
+      <c r="X24">
+        <v>0.6863834042835359</v>
+      </c>
+      <c r="Y24">
+        <v>-4.43550847563459</v>
+      </c>
+      <c r="Z24">
+        <v>-0.0985943302512169</v>
+      </c>
+      <c r="AA24">
+        <v>45407904</v>
+      </c>
+      <c r="AB24">
+        <v>1.3</v>
+      </c>
+      <c r="AC24">
+        <v>-0.697565734386444</v>
+      </c>
+      <c r="AD24">
+        <v>-0.482351809740067</v>
+      </c>
+      <c r="AE24">
         <v>11.0858180930687</v>
       </c>
-      <c r="F24">
+      <c r="AF24">
+        <v>44795335171.5152</v>
+      </c>
+      <c r="AG24">
+        <v>4.75930856415363</v>
+      </c>
+      <c r="AH24">
+        <v>31.5477080051071</v>
+      </c>
+      <c r="AI24">
         <v>6.805</v>
       </c>
+      <c r="AJ24">
+        <v>92.34699999999999</v>
+      </c>
+      <c r="AK24">
+        <v>0.546316981315613</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:37">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
+        <v>18.3130321618414</v>
+      </c>
+      <c r="C25">
+        <v>114.601250853291</v>
+      </c>
+      <c r="D25">
+        <v>3.5490485353568</v>
+      </c>
+      <c r="E25">
+        <v>-0.360883951187134</v>
+      </c>
+      <c r="F25">
+        <v>-3.21189377266388</v>
+      </c>
+      <c r="G25">
+        <v>15.437576647908</v>
+      </c>
+      <c r="H25">
+        <v>12.7492457826544</v>
+      </c>
+      <c r="I25">
+        <v>42.0664911888795</v>
+      </c>
+      <c r="J25">
+        <v>266167259703.1</v>
+      </c>
+      <c r="K25">
         <v>-1.61100162090189</v>
       </c>
-      <c r="C25">
+      <c r="L25">
+        <v>30082.3045247325</v>
+      </c>
+      <c r="M25">
+        <v>14187.4827252965</v>
+      </c>
+      <c r="N25">
+        <v>-1.89294979737558</v>
+      </c>
+      <c r="O25">
+        <v>42.4</v>
+      </c>
+      <c r="P25">
+        <v>-0.377517342567444</v>
+      </c>
+      <c r="Q25">
+        <v>16.3874689950096</v>
+      </c>
+      <c r="R25">
+        <v>21.1189070510753</v>
+      </c>
+      <c r="S25">
+        <v>17.8684969726739</v>
+      </c>
+      <c r="T25">
+        <v>13.8912663507893</v>
+      </c>
+      <c r="U25">
         <v>133.488935594175</v>
       </c>
-      <c r="D25">
+      <c r="V25">
         <v>7.28994415748098</v>
       </c>
-      <c r="E25">
+      <c r="W25">
+        <v>77.395</v>
+      </c>
+      <c r="X25">
+        <v>0.472747196738259</v>
+      </c>
+      <c r="Y25">
+        <v>-3.61371624476762</v>
+      </c>
+      <c r="Z25">
+        <v>-0.127517908811569</v>
+      </c>
+      <c r="AA25">
+        <v>45538401</v>
+      </c>
+      <c r="AB25">
+        <v>1.2</v>
+      </c>
+      <c r="AC25">
+        <v>-0.482535392045975</v>
+      </c>
+      <c r="AD25">
+        <v>-0.410826534032822</v>
+      </c>
+      <c r="AE25">
         <v>9.98093648141313</v>
       </c>
-      <c r="F25">
+      <c r="AF25">
+        <v>23080560550.2946</v>
+      </c>
+      <c r="AG25">
+        <v>2.45755251575411</v>
+      </c>
+      <c r="AH25">
+        <v>26.6405121334437</v>
+      </c>
+      <c r="AI25">
         <v>6.139</v>
       </c>
+      <c r="AJ25">
+        <v>92.46299999999999</v>
+      </c>
+      <c r="AK25">
+        <v>0.533921837806702</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:37">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="C26">
+        <v>23.9686598013467</v>
+      </c>
+      <c r="F26">
+        <v>0.900309383642294</v>
+      </c>
+      <c r="G26">
+        <v>15.2393982039314</v>
+      </c>
+      <c r="H26">
+        <v>15.3342337389676</v>
+      </c>
+      <c r="K26">
         <v>-1.71910514722377</v>
       </c>
-      <c r="C26">
+      <c r="L26">
+        <v>30175.5359656699</v>
+      </c>
+      <c r="M26">
+        <v>13858.2039802008</v>
+      </c>
+      <c r="N26">
+        <v>-2.05840275449496</v>
+      </c>
+      <c r="O26">
+        <v>42.4</v>
+      </c>
+      <c r="Q26">
+        <v>15.0308136208788</v>
+      </c>
+      <c r="T26">
+        <v>12.8251676959106</v>
+      </c>
+      <c r="U26">
         <v>219.883929014578</v>
       </c>
-      <c r="F26">
+      <c r="AA26">
+        <v>45696159</v>
+      </c>
+      <c r="AB26">
+        <v>1</v>
+      </c>
+      <c r="AF26">
+        <v>29559610350.7831</v>
+      </c>
+      <c r="AG26">
+        <v>3.55326074207238</v>
+      </c>
+      <c r="AH26">
+        <v>28.1594014348782</v>
+      </c>
+      <c r="AI26">
         <v>7.876</v>
+      </c>
+      <c r="AJ26">
+        <v>92.57899999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ARG_WB_timeseries.xlsx
+++ b/ARG_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -443,12 +446,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X36"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -519,8 +522,11 @@
       <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -543,43 +549,46 @@
         <v>34902990</v>
       </c>
       <c r="I2">
+        <v>141352654305.163</v>
+      </c>
+      <c r="J2">
         <v>-2.46721377810472</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>4315.33403111588</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>3.13542839161188</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>10.3254404487432</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>10.3875396339054</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>4.63132240741775</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>8.65453523501721</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>-0.107803024709003</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>4.83851314669697</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>6222040362.99099</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>5.69957895846503</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <v>14.9908589999441</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:25">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -602,49 +611,52 @@
         <v>49385690</v>
       </c>
       <c r="I3">
+        <v>189719984268.485</v>
+      </c>
+      <c r="J3">
         <v>9.133110567389609</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>5709.24784079504</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>46.8</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>3.32176128752774</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>11.2055409345172</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>11.1620910357746</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>6.07801081056698</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>11.0514735626967</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>-0.229466322749109</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>5.00823654744009</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>7462543636.08691</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>5.09620553340786</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>13.7530541588891</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <v>5.44</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:25">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -667,49 +679,52 @@
         <v>1165914300</v>
       </c>
       <c r="I4">
+        <v>228778917308.17</v>
+      </c>
+      <c r="J4">
         <v>7.93729155643076</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>6789.99611136495</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>45.5</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2.97553802761558</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>11.8011099217048</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>12.2806411476509</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>8.132793114315639</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>9.80266060465569</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>0.264562866283836</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>5.54792213441138</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>11447031156.7334</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>5.70506107278321</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>14.730980586353</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>6.36</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:25">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -732,49 +747,52 @@
         <v>705070000</v>
       </c>
       <c r="I5">
+        <v>236741715015.015</v>
+      </c>
+      <c r="J5">
         <v>8.206979072212279</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>6931.85596375876</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>44.8</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>13.5103784728742</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>14.2818561185834</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>15.0995556252854</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>9.313799914075631</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>7.60836419725674</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>0.483203369491258</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>8.01513800555669</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>15499431243.972</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>6.74386056512176</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>16.223151447784</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <v>10.1</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:25">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -797,49 +815,52 @@
         <v>1012844000</v>
       </c>
       <c r="I6">
+        <v>257440000000</v>
+      </c>
+      <c r="J6">
         <v>5.83620070368526</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>7437.56242327594</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>45.9</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>13.1869043660659</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>14.9007924176507</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>14.8638517712865</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>10.6043971410814</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>8.321037731422351</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>-0.32605655686762</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>8.12643722809198</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>16003265688.189</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>5.59678188654751</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>18.1343458669981</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>11.76</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:25">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -862,49 +883,52 @@
         <v>1497149000</v>
       </c>
       <c r="I7">
+        <v>258031750000</v>
+      </c>
+      <c r="J7">
         <v>-2.84520961057079</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>7357.6162773788</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>48.9</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>13.3494556774505</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>15.5112306915719</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>14.0262971514164</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>10.0910128307854</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>10.2016545114294</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>-1.71796687810705</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>8.054357651723089</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>15979453701.6387</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>5.47248285450445</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>19.7714230903755</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>18.8</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:25">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -930,52 +954,55 @@
         <v>1600749000</v>
       </c>
       <c r="I8">
+        <v>272149750000</v>
+      </c>
+      <c r="J8">
         <v>5.52668982715234</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>7663.21271287469</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>49.5</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>12.5016776609201</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>15.1655476442657</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>13.0408350549651</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>11.0778716497076</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>11.2133840525283</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>-2.33400912549065</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>0.111376881599426</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>8.17178777492906</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>19719017351.0624</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>5.89789511152116</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>21.5064684057215</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>17.11</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:25">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -998,49 +1025,52 @@
         <v>3652818000</v>
       </c>
       <c r="I9">
+        <v>292859000000</v>
+      </c>
+      <c r="J9">
         <v>8.1110467707457</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>8146.78710021431</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>49.1</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>12.0620142457633</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>15.0142218610321</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>13.6002991200544</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>12.7753287418177</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>13.0351030804744</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>-1.65752119620705</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <v>8.690086355549941</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>22424600096.7817</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>5.47566058156948</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>23.3361788437439</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>14.82</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:25">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1066,52 +1096,55 @@
         <v>2325477000</v>
       </c>
       <c r="I10">
+        <v>298948250000</v>
+      </c>
+      <c r="J10">
         <v>3.85017885156228</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>8218.992127646819</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>50.7</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>12.4947749986829</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>15.0988005449104</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>13.7561266874785</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>12.934446011977</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>14.7114600687675</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>-1.58616081545886</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>-0.134649589657784</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>9.03052618638845</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>24855741222.2541</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>5.69914835773996</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>23.3500279730689</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>12.65</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:25">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1134,49 +1167,52 @@
         <v>1730283000</v>
       </c>
       <c r="I11">
+        <v>283523000000</v>
+      </c>
+      <c r="J11">
         <v>-3.38545704063269</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>7705.54288252851</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>49.8</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>13.7232114149469</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>16.7436856974566</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>14.0111384261594</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>11.5555704475475</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>17.2745311993124</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>-2.92441883021836</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>9.076124335591819</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>26350163486.3723</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>6.80464213303423</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>21.3827449624898</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <v>14.05</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:25">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1202,52 +1238,55 @@
         <v>901028199.3378561</v>
       </c>
       <c r="I12">
+        <v>284203750000</v>
+      </c>
+      <c r="J12">
         <v>-0.78899893905691</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>7637.01489203628</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>51</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>13.7841913064131</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>16.8328883767368</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>14.1776102532074</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>11.6360695451767</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>20.1040140301883</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>-2.77220128165093</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>0.0958238765597343</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>9.622603501889049</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>25152117244.4134</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>6.28322204626375</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>22.6224447777343</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:25">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1270,49 +1309,52 @@
         <v>160876687.495159</v>
       </c>
       <c r="I13">
+        <v>268696750000</v>
+      </c>
+      <c r="J13">
         <v>-4.40883968258557</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>7141.47507662826</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>53.3</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>14.1562743129569</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>16.9923529034125</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>13.7775019608536</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>10.2732473690136</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>22.2743490173661</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>-3.31954145332982</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>9.324898793900561</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>14555552759.6102</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>4.29371406025342</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>21.8522554515453</v>
       </c>
-      <c r="X13">
+      <c r="Y13">
         <v>17.32</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:25">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1338,52 +1380,55 @@
         <v>-627140000</v>
       </c>
       <c r="I14">
+        <v>97724004251.8602</v>
+      </c>
+      <c r="J14">
         <v>-10.8944848285903</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>2569.69963519124</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>53.8</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>12.235247296692</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>19.6771706443151</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>14.0561136349095</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>13.370127359396</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>34.2849338854665</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>-5.70628319150298</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>-0.776545405387878</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>9.81895834666325</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>10492424818.7375</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>5.27543170673442</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>41.7527243585642</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>19.59</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:25">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1409,52 +1454,55 @@
         <v>773780000</v>
       </c>
       <c r="I15">
+        <v>127586973492.177</v>
+      </c>
+      <c r="J15">
         <v>8.837040795769241</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>3320.47775133903</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>51</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>11.4380567929249</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>19.8373029880995</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>17.1997019513553</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>14.7138051046861</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>30.0083948621788</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>-2.82936804297577</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>-0.359838128089905</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>12.5187797002949</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>14157284136.3645</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>5.70013745215417</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>40.6447480311085</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <v>15.36</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:25">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1480,52 +1528,55 @@
         <v>675990000</v>
       </c>
       <c r="I16">
+        <v>164657930452.787</v>
+      </c>
+      <c r="J16">
         <v>9.02957330068152</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>4242.02099089422</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>48.5</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>11.114636067696</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>16.8763416365527</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>16.7347777696665</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>16.8450266849578</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>26.3142537893684</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>-0.425276316786125</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>-0.610934913158417</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>13.1007798994386</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>19659591803.9788</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>5.77837779911896</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>40.692646108947</v>
       </c>
-      <c r="X16">
+      <c r="Y16">
         <v>13.522</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:25">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1551,43 +1602,46 @@
         <v>1311060000</v>
       </c>
       <c r="I17">
+        <v>198737095012.282</v>
+      </c>
+      <c r="J17">
         <v>8.85165992013437</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>5067.65342293276</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>47.8</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>12.1418612359575</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>16.6216575161027</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>17.3053942367662</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>-0.0417749434709549</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>13.1031756459852</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>28081718501.5579</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>7.26029776298214</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>40.5512709706238</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <v>11.506</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:25">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1613,43 +1667,46 @@
         <v>2438720720.56097</v>
       </c>
       <c r="I18">
+        <v>232557260817.308</v>
+      </c>
+      <c r="J18">
         <v>8.047151500430269</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>5869.38028970204</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>46.4</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>12.4294153726307</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>17.2017551603052</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>17.4067852681036</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>0.00196776282973588</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>12.8788866954319</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>32022297112.9806</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>7.02897239370493</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>40.4334798719151</v>
       </c>
-      <c r="X18">
+      <c r="Y18">
         <v>10.078</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:25">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1675,43 +1732,46 @@
         <v>1504232961.34457</v>
       </c>
       <c r="I19">
+        <v>287530508430.568</v>
+      </c>
+      <c r="J19">
         <v>9.00765087504757</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>7185.25155147027</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>46.3</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>12.9893238963619</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>17.9300729987004</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>18.2824203070644</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>0.0977966338396072</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>12.4482684483004</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>46149456855.7802</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>8.171534286186461</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>40.945170618571</v>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <v>8.470000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:25">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1737,43 +1797,46 @@
         <v>1390934588.87756</v>
       </c>
       <c r="I20">
+        <v>361558037110.419</v>
+      </c>
+      <c r="J20">
         <v>4.05723310346406</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>8944.110265735701</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>45</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>13.6335132595631</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>18.9717341522181</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>18.341772996414</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>-0.0877556875348091</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>13.3178463574032</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>46385380206.9801</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>6.71425831138327</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>40.4026733790382</v>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <v>7.837</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:25">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1799,43 +1862,46 @@
         <v>711546403.745669</v>
       </c>
       <c r="I21">
+        <v>332976484577.619</v>
+      </c>
+      <c r="J21">
         <v>-5.91852507634947</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>8150.23527028221</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>43.8</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>15.903896746884</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>20.1360210279783</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>14.4961418494061</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>-0.234854578971863</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>12.3830415594157</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>48006988635.3253</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>9.067499928752429</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>34.0571269054879</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>8.645</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:25">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1861,43 +1927,46 @@
         <v>964760680.391807</v>
       </c>
       <c r="I22">
+        <v>423627422092.49</v>
+      </c>
+      <c r="J22">
         <v>10.1253981561002</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>10260.1313108254</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>43.7</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>15.1637178886417</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>21.2413164267537</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>16.0371898581987</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>-0.0847978666424751</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>12.8530426903255</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>52207549724.0928</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>7.27697103967374</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>34.9710132635696</v>
       </c>
-      <c r="X22">
+      <c r="Y22">
         <v>7.714</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:25">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -1923,43 +1992,46 @@
         <v>1488000000</v>
       </c>
       <c r="I23">
+        <v>530158122010.442</v>
+      </c>
+      <c r="J23">
         <v>6.00395169280579</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>12704.2831819684</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>42.7</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>15.6889565165983</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>20.196408074281</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>16.7569458546489</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>0.158993661403656</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>12.6636277012315</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>46265800525.8807</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>5.20195157798821</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>35.2061549999644</v>
       </c>
-      <c r="X23">
+      <c r="Y23">
         <v>7.18</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:25">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -1985,43 +2057,46 @@
         <v>1054849578.05632</v>
       </c>
       <c r="I24">
+        <v>545982375701.128</v>
+      </c>
+      <c r="J24">
         <v>-1.0264204544321</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>12949.717486654</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>41.4</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>16.6454378106252</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>21.182234604867</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>14.2886829096862</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>0.103040546178818</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>12.9528415127413</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>43223270863.843</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>5.21829041219894</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>30.5265423717108</v>
       </c>
-      <c r="X24">
+      <c r="Y24">
         <v>7.217</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:25">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2047,43 +2122,46 @@
         <v>889972858.727091</v>
       </c>
       <c r="I25">
+        <v>552025140252.246</v>
+      </c>
+      <c r="J25">
         <v>2.40532378079436</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>12963.675773326</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>41.1</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>16.8062377968797</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>21.5652829643596</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>14.7167556136651</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>0.0653142631053925</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>12.4529027558077</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>30533919650.6264</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>3.46015205462158</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>29.3339290021037</v>
       </c>
-      <c r="X25">
+      <c r="Y25">
         <v>7.1</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:25">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2109,52 +2187,55 @@
         <v>1920541433.10504</v>
       </c>
       <c r="I26">
+        <v>526319673731.638</v>
+      </c>
+      <c r="J26">
         <v>-2.51261532081394</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>12233.1444119186</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>41.8</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>16.9498757371062</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>24.5697808575806</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>22.3322943705014</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>14.0013150558519</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>7.75788916526639</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>-2.90614606577065</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>-0.00512187136337161</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>12.6109666067191</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>31410813269.5239</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>3.96299919336678</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>28.4067936452275</v>
       </c>
-      <c r="X26">
+      <c r="Y26">
         <v>7.268</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:25">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2180,49 +2261,52 @@
         <v>875233227.3542579</v>
       </c>
       <c r="I27">
+        <v>594749285413.212</v>
+      </c>
+      <c r="J27">
         <v>2.73115982828944</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>13679.6264980954</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>18.098379759087</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>25.0083932347048</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>22.1490803040164</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>11.7805740385254</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>7.37421073749561</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>-3.39011034719535</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>0.00876413471996784</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>12.3365069418291</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>25520565580.4894</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>3.36214425707702</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>22.4862260889792</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>7.579</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:25">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2248,52 +2332,55 @@
         <v>1786530934.74804</v>
       </c>
       <c r="I28">
+        <v>557532320662.955</v>
+      </c>
+      <c r="J28">
         <v>-2.08032784377811</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>12699.9623137756</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>42.3</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>17.6545781863509</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>26.1799164832469</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>21.2567013071388</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>13.5667926798789</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>11.3900941602608</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>-5.33377782706346</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>0.197749897837639</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>12.0972836411962</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>38414518491.6132</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>5.09719624487539</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>26.0938878488799</v>
       </c>
-      <c r="X28">
+      <c r="Y28">
         <v>8.085000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:25">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2319,52 +2406,55 @@
         <v>1155630218.02452</v>
       </c>
       <c r="I29">
+        <v>643628393281.364</v>
+      </c>
+      <c r="J29">
         <v>2.81850297775918</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>14532.5009308511</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>41.4</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>17.6968939223042</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>24.2825320419979</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>19.3371239744582</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>13.9693177780045</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>9.419814018022439</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>-5.51824569508007</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>0.162542164325714</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>10.939623860491</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>55314409205.2189</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>6.05038766582561</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>25.2896011376779</v>
       </c>
-      <c r="X29">
+      <c r="Y29">
         <v>8.347</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:25">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2390,55 +2480,58 @@
         <v>1725981572.7057</v>
       </c>
       <c r="I30">
+        <v>524819892360.176</v>
+      </c>
+      <c r="J30">
         <v>-2.61739646282038</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>11752.7998922979</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>41.7</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>15.8050971558947</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>22.6709430512171</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>17.7024488717292</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>16.3258502050892</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>34.2772237131003</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>12.8793045637226</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>-5.33635226717988</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>0.00690981233492494</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>9.79144712037089</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>66221501691.4418</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>7.11111211150086</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>30.7625359549926</v>
       </c>
-      <c r="X30">
+      <c r="Y30">
         <v>9.220000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:24">
+    <row r="31" spans="1:25">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2464,55 +2557,58 @@
         <v>1522728151.79532</v>
       </c>
       <c r="I31">
+        <v>447754683615.225</v>
+      </c>
+      <c r="J31">
         <v>-2.00086100285785</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>9955.97478680428</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>43.3</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>16.4432415862976</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>22.0364845686943</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>17.7888990504455</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>14.7057366680037</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>53.5483043492339</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>15.7967986276777</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>-4.92889704924096</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>-0.0978230908513069</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>10.3919973375121</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>44880566052.3703</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>5.94220121846315</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>32.6306150458499</v>
       </c>
-      <c r="X31">
+      <c r="Y31">
         <v>9.843</v>
       </c>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:25">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2538,55 +2634,58 @@
         <v>1177176908.60545</v>
       </c>
       <c r="I32">
+        <v>385740508436.965</v>
+      </c>
+      <c r="J32">
         <v>-9.900484813646401</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>8535.59938004389</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>42.7</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>16.8730073837365</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>25.8405452538391</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>17.4777322783093</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>13.5982843701675</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>42.0150947376509</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>7.50264305918987</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>-8.6954919523039</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>-0.0719974040985107</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>10.70812114449</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>39403734630.1228</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>7.09405401009515</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>30.203698807416</v>
       </c>
-      <c r="X32">
+      <c r="Y32">
         <v>11.461</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:25">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2612,55 +2711,58 @@
         <v>1543861737.75886</v>
       </c>
       <c r="I33">
+        <v>486564085480.036</v>
+      </c>
+      <c r="J33">
         <v>10.4418119882506</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>10738.0179223384</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>42.4</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>15.9158179423023</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>22.8967903877811</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>18.0764989044589</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>15.0119803984295</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>48.4093786255199</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>6.52367466313931</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>-4.37239542495983</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>0.000530058634467423</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>11.3410740330927</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>39653498610.7828</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>5.6049034262494</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>33.078689567466</v>
       </c>
-      <c r="X33">
+      <c r="Y33">
         <v>8.736000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:25">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2686,55 +2788,58 @@
         <v>2089836583.05669</v>
       </c>
       <c r="I34">
+        <v>632790070063.124</v>
+      </c>
+      <c r="J34">
         <v>5.26987967384072</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>13935.6811110049</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>40.7</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>15.8356571842994</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>21.9068187207194</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>17.9272315382489</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>15.2996935612041</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>72.430757531824</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>7.76084028840006</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>-4.43550847563459</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>-0.0985943302512169</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>11.0858180930687</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>44795335171.5152</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>4.75930856415363</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>31.5477080051071</v>
       </c>
-      <c r="X34">
+      <c r="Y34">
         <v>6.805</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:25">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2760,55 +2865,58 @@
         <v>3023263070.30906</v>
       </c>
       <c r="I35">
+        <v>646075277525.125</v>
+      </c>
+      <c r="J35">
         <v>-1.61100162090189</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>14187.4827252965</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>42.4</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>16.3874689950096</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>21.1189070510753</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>17.8684969726739</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>13.8912663507893</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>133.488935594175</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>7.28994415748098</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>-3.61371624476762</v>
       </c>
-      <c r="S35">
+      <c r="T35">
         <v>-0.127517908811569</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>9.98093648141313</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>23080560550.2946</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>2.45755251575411</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>26.6405121334437</v>
       </c>
-      <c r="X35">
+      <c r="Y35">
         <v>6.139</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:25">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2825,33 +2933,36 @@
         <v>2756722688.00138</v>
       </c>
       <c r="I36">
+        <v>633266692533.689</v>
+      </c>
+      <c r="J36">
         <v>-1.71910514722377</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>13858.2039802008</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>42.4</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>15.0308136208788</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>12.8251676959106</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>219.883929014578</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>29559610350.7831</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>3.55326074207238</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>28.1594014348782</v>
       </c>
-      <c r="X36">
+      <c r="Y36">
         <v>7.876</v>
       </c>
     </row>

--- a/ARG_WB_timeseries.xlsx
+++ b/ARG_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CE7676-B99C-D948-828E-C8D50AC85805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,7 +472,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -503,16 +480,16 @@
         <v>-0.172407656908035</v>
       </c>
       <c r="C2">
-        <v>-3.1599223770367599</v>
+        <v>-3.15992237703676</v>
       </c>
       <c r="D2">
-        <v>10.986375232557601</v>
+        <v>10.9863752325576</v>
       </c>
       <c r="E2">
-        <v>-0.78899893905690999</v>
+        <v>-0.78899893905691</v>
       </c>
       <c r="F2">
-        <v>7637.0148920362799</v>
+        <v>7637.01489203628</v>
       </c>
       <c r="G2">
         <v>16.8328883767368</v>
@@ -521,49 +498,48 @@
         <v>14.1776102532074</v>
       </c>
       <c r="I2">
-        <v>11.636069545176699</v>
+        <v>11.6360695451767</v>
       </c>
       <c r="J2">
         <v>-0.9</v>
       </c>
       <c r="K2">
-        <v>20.104014030188299</v>
+        <v>20.1040140301883</v>
       </c>
       <c r="L2">
         <v>-2.77220128165093</v>
       </c>
       <c r="M2">
-        <v>9.5823876559734303E-2</v>
+        <v>0.0958238765597343</v>
       </c>
       <c r="N2">
-        <v>9.6226035018890492</v>
+        <v>9.622603501889049</v>
       </c>
       <c r="O2">
-        <v>22.622444777734302</v>
+        <v>22.6224447777343</v>
       </c>
       <c r="P2">
-        <v>40.799999999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
         <v>-1.40694788500181</v>
       </c>
       <c r="D3">
-        <v>11.579008082531701</v>
+        <v>11.5790080825317</v>
       </c>
       <c r="E3">
-        <v>-4.4088396825855698</v>
+        <v>-4.40883968258557</v>
       </c>
       <c r="F3">
-        <v>7141.4750766282596</v>
+        <v>7141.47507662826</v>
       </c>
       <c r="G3">
-        <v>16.992352903412499</v>
+        <v>16.9923529034125</v>
       </c>
       <c r="H3">
         <v>13.7775019608536</v>
@@ -572,17 +548,16 @@
         <v>10.2732473690136</v>
       </c>
       <c r="J3">
-        <v>-1.1000000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="K3">
-        <v>22.274349017366099</v>
+        <v>22.2743490173661</v>
       </c>
       <c r="L3">
         <v>-3.31954145332982</v>
       </c>
-      <c r="M3" s="2"/>
       <c r="N3">
-        <v>9.3248987939005605</v>
+        <v>9.324898793900561</v>
       </c>
       <c r="O3">
         <v>21.8522554515453</v>
@@ -591,80 +566,80 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>-0.41705572605133101</v>
+        <v>-0.417055726051331</v>
       </c>
       <c r="C4">
-        <v>8.9707846778424702</v>
+        <v>8.97078467784247</v>
       </c>
       <c r="D4">
         <v>28.3825969991682</v>
       </c>
       <c r="E4">
-        <v>-10.894484828590301</v>
+        <v>-10.8944848285903</v>
       </c>
       <c r="F4">
-        <v>2569.6996351912398</v>
+        <v>2569.69963519124</v>
       </c>
       <c r="G4">
-        <v>19.677170644315101</v>
+        <v>19.6771706443151</v>
       </c>
       <c r="H4">
-        <v>14.056113634909501</v>
+        <v>14.0561136349095</v>
       </c>
       <c r="I4">
-        <v>13.370127359395999</v>
+        <v>13.370127359396</v>
       </c>
       <c r="J4">
         <v>25.9</v>
       </c>
       <c r="K4">
-        <v>34.284933885466501</v>
+        <v>34.2849338854665</v>
       </c>
       <c r="L4">
-        <v>-5.7062831915029797</v>
+        <v>-5.70628319150298</v>
       </c>
       <c r="M4">
-        <v>-0.77654540538787797</v>
+        <v>-0.776545405387878</v>
       </c>
       <c r="N4">
-        <v>9.8189583466632495</v>
+        <v>9.81895834666325</v>
       </c>
       <c r="O4">
-        <v>41.752724358564201</v>
+        <v>41.7527243585642</v>
       </c>
       <c r="P4">
-        <v>147.19999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+        <v>147.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>-0.47997680306434598</v>
+        <v>-0.479976803064346</v>
       </c>
       <c r="C5">
-        <v>6.3799068017701099</v>
+        <v>6.37990680177011</v>
       </c>
       <c r="D5">
         <v>25.9309429264224</v>
       </c>
       <c r="E5">
-        <v>8.8370407957692407</v>
+        <v>8.837040795769241</v>
       </c>
       <c r="F5">
         <v>3320.47775133903</v>
       </c>
       <c r="G5">
-        <v>19.837302988099498</v>
+        <v>19.8373029880995</v>
       </c>
       <c r="H5">
-        <v>17.199701951355301</v>
+        <v>17.1997019513553</v>
       </c>
       <c r="I5">
         <v>14.7138051046861</v>
@@ -676,72 +651,72 @@
         <v>30.0083948621788</v>
       </c>
       <c r="L5">
-        <v>-2.8293680429757702</v>
+        <v>-2.82936804297577</v>
       </c>
       <c r="M5">
-        <v>-0.35983812808990501</v>
+        <v>-0.359838128089905</v>
       </c>
       <c r="N5">
         <v>12.5187797002949</v>
       </c>
       <c r="O5">
-        <v>40.644748031108499</v>
+        <v>40.6447480311085</v>
       </c>
       <c r="P5">
         <v>125.2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>-0.41440954804420499</v>
+        <v>-0.414409548044205</v>
       </c>
       <c r="C6">
-        <v>1.9505832431927299</v>
+        <v>1.95058324319273</v>
       </c>
       <c r="D6">
-        <v>23.847619423989201</v>
+        <v>23.8476194239892</v>
       </c>
       <c r="E6">
-        <v>9.0295733006815198</v>
+        <v>9.02957330068152</v>
       </c>
       <c r="F6">
-        <v>4242.0209908942197</v>
+        <v>4242.02099089422</v>
       </c>
       <c r="G6">
-        <v>16.876341636552699</v>
+        <v>16.8763416365527</v>
       </c>
       <c r="H6">
-        <v>16.734777769666501</v>
+        <v>16.7347777696665</v>
       </c>
       <c r="I6">
-        <v>16.845026684957801</v>
+        <v>16.8450266849578</v>
       </c>
       <c r="J6">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>26.314253789368401</v>
+        <v>26.3142537893684</v>
       </c>
       <c r="L6">
-        <v>-0.42527631678612499</v>
+        <v>-0.425276316786125</v>
       </c>
       <c r="M6">
-        <v>-0.61093491315841697</v>
+        <v>-0.610934913158417</v>
       </c>
       <c r="N6">
-        <v>13.100779899438599</v>
+        <v>13.1007798994386</v>
       </c>
       <c r="O6">
-        <v>40.692646108947002</v>
+        <v>40.692646108947</v>
       </c>
       <c r="P6">
         <v>117.9</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -749,229 +724,219 @@
         <v>-0.377738356590271</v>
       </c>
       <c r="C7">
-        <v>2.6536314217907302</v>
+        <v>2.65363142179073</v>
       </c>
       <c r="D7">
         <v>23.2458767338576</v>
       </c>
       <c r="E7">
-        <v>8.8516599201343702</v>
+        <v>8.85165992013437</v>
       </c>
       <c r="F7">
-        <v>5067.6534229327599</v>
-      </c>
-      <c r="G7" s="2"/>
+        <v>5067.65342293276</v>
+      </c>
       <c r="H7">
-        <v>16.621657516102701</v>
+        <v>16.6216575161027</v>
       </c>
       <c r="I7">
-        <v>17.305394236766201</v>
+        <v>17.3053942367662</v>
       </c>
       <c r="J7">
         <v>9.6</v>
       </c>
-      <c r="K7" s="2"/>
       <c r="L7">
         <v>3.3</v>
       </c>
       <c r="M7">
-        <v>-4.1774943470954902E-2</v>
+        <v>-0.0417749434709549</v>
       </c>
       <c r="N7">
         <v>13.1031756459852</v>
       </c>
       <c r="O7">
-        <v>40.551270970623797</v>
+        <v>40.5512709706238</v>
       </c>
       <c r="P7">
         <v>80.3</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>-0.33123853802681003</v>
+        <v>-0.33123853802681</v>
       </c>
       <c r="C8">
-        <v>2.7944956426494301</v>
+        <v>2.79449564264943</v>
       </c>
       <c r="D8">
-        <v>23.026694603811499</v>
+        <v>23.0266946038115</v>
       </c>
       <c r="E8">
-        <v>8.0471515004302692</v>
+        <v>8.047151500430269</v>
       </c>
       <c r="F8">
-        <v>5869.3802897020396</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>5869.38028970204</v>
+      </c>
       <c r="H8">
-        <v>17.201755160305201</v>
+        <v>17.2017551603052</v>
       </c>
       <c r="I8">
-        <v>17.406785268103601</v>
+        <v>17.4067852681036</v>
       </c>
       <c r="J8">
         <v>10.9</v>
       </c>
-      <c r="K8" s="2"/>
       <c r="L8">
         <v>1.7</v>
       </c>
       <c r="M8">
-        <v>1.9677628297358799E-3</v>
+        <v>0.00196776282973588</v>
       </c>
       <c r="N8">
         <v>12.8788866954319</v>
       </c>
       <c r="O8">
-        <v>40.433479871915097</v>
+        <v>40.4334798719151</v>
       </c>
       <c r="P8">
         <v>70.8</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>-0.37212207913398698</v>
+        <v>-0.372122079133987</v>
       </c>
       <c r="C9">
-        <v>2.1036160391819001</v>
+        <v>2.1036160391819</v>
       </c>
       <c r="D9">
-        <v>22.662750311506599</v>
+        <v>22.6627503115066</v>
       </c>
       <c r="E9">
-        <v>9.0076508750475703</v>
+        <v>9.00765087504757</v>
       </c>
       <c r="F9">
         <v>7185.25155147027</v>
       </c>
-      <c r="G9" s="2"/>
       <c r="H9">
         <v>17.9300729987004</v>
       </c>
       <c r="I9">
-        <v>18.282420307064399</v>
+        <v>18.2824203070644</v>
       </c>
       <c r="J9">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>8.800000000000001</v>
+      </c>
       <c r="L9">
         <v>0.8</v>
       </c>
       <c r="M9">
-        <v>9.7796633839607197E-2</v>
+        <v>0.0977966338396072</v>
       </c>
       <c r="N9">
         <v>12.4482684483004</v>
       </c>
       <c r="O9">
-        <v>40.945170618570998</v>
+        <v>40.945170618571</v>
       </c>
       <c r="P9">
         <v>62.1</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
-        <v>-0.43487501144409202</v>
+        <v>-0.434875011444092</v>
       </c>
       <c r="C10">
-        <v>1.4994014161423399</v>
+        <v>1.49940141614234</v>
       </c>
       <c r="D10">
-        <v>22.060900382624201</v>
+        <v>22.0609003826242</v>
       </c>
       <c r="E10">
-        <v>4.0572331034640596</v>
+        <v>4.05723310346406</v>
       </c>
       <c r="F10">
-        <v>8944.1102657357005</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>8944.110265735701</v>
+      </c>
       <c r="H10">
-        <v>18.971734152218101</v>
+        <v>18.9717341522181</v>
       </c>
       <c r="I10">
-        <v>18.341772996414001</v>
+        <v>18.341772996414</v>
       </c>
       <c r="J10">
         <v>8.6</v>
       </c>
-      <c r="K10" s="2"/>
       <c r="L10">
         <v>0.4</v>
       </c>
       <c r="M10">
-        <v>-8.7755687534809099E-2</v>
+        <v>-0.0877556875348091</v>
       </c>
       <c r="N10">
         <v>13.3178463574032</v>
       </c>
       <c r="O10">
-        <v>40.402673379038198</v>
+        <v>40.4026733790382</v>
       </c>
       <c r="P10">
         <v>53.8</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>-0.44547510147094699</v>
+        <v>-0.445475101470947</v>
       </c>
       <c r="C11">
-        <v>2.1785669619099002</v>
+        <v>2.1785669619099</v>
       </c>
       <c r="D11">
-        <v>19.560985056081801</v>
+        <v>19.5609850560818</v>
       </c>
       <c r="E11">
-        <v>-5.9185250763494697</v>
+        <v>-5.91852507634947</v>
       </c>
       <c r="F11">
         <v>8150.23527028221</v>
       </c>
-      <c r="G11" s="2"/>
       <c r="H11">
-        <v>20.136021027978298</v>
+        <v>20.1360210279783</v>
       </c>
       <c r="I11">
-        <v>14.496141849406101</v>
+        <v>14.4961418494061</v>
       </c>
       <c r="J11">
         <v>6.3</v>
       </c>
-      <c r="K11" s="2"/>
       <c r="L11">
         <v>-1.8</v>
       </c>
       <c r="M11">
-        <v>-0.23485457897186299</v>
+        <v>-0.234854578971863</v>
       </c>
       <c r="N11">
         <v>12.3830415594157</v>
       </c>
       <c r="O11">
-        <v>34.057126905487898</v>
+        <v>34.0571269054879</v>
       </c>
       <c r="P11">
         <v>55.4</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -979,10 +944,10 @@
         <v>-0.355230033397675</v>
       </c>
       <c r="C12">
-        <v>-0.38311869973713297</v>
+        <v>-0.383118699737133</v>
       </c>
       <c r="D12">
-        <v>18.933823405370902</v>
+        <v>18.9338234053709</v>
       </c>
       <c r="E12">
         <v>10.1253981561002</v>
@@ -990,39 +955,37 @@
       <c r="F12">
         <v>10260.1313108254</v>
       </c>
-      <c r="G12" s="2"/>
       <c r="H12">
-        <v>21.241316426753698</v>
+        <v>21.2413164267537</v>
       </c>
       <c r="I12">
-        <v>16.037189858198701</v>
+        <v>16.0371898581987</v>
       </c>
       <c r="J12">
         <v>10.5</v>
       </c>
-      <c r="K12" s="2"/>
       <c r="L12">
         <v>-1.4</v>
       </c>
       <c r="M12">
-        <v>-8.47978666424751E-2</v>
+        <v>-0.0847978666424751</v>
       </c>
       <c r="N12">
         <v>12.8530426903255</v>
       </c>
       <c r="O12">
-        <v>34.971013263569603</v>
+        <v>34.9710132635696</v>
       </c>
       <c r="P12">
         <v>43.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>-0.36409851908683799</v>
+        <v>-0.364098519086838</v>
       </c>
       <c r="C13">
         <v>-1.00728084144866</v>
@@ -1031,60 +994,57 @@
         <v>18.4492091453155</v>
       </c>
       <c r="E13">
-        <v>6.0039516928057903</v>
+        <v>6.00395169280579</v>
       </c>
       <c r="F13">
         <v>12704.2831819684</v>
       </c>
-      <c r="G13" s="2"/>
       <c r="H13">
-        <v>20.196408074280999</v>
+        <v>20.196408074281</v>
       </c>
       <c r="I13">
-        <v>16.756945854648901</v>
+        <v>16.7569458546489</v>
       </c>
       <c r="J13">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>9.800000000000001</v>
+      </c>
       <c r="L13">
         <v>-2.7</v>
       </c>
       <c r="M13">
-        <v>0.15899366140365601</v>
+        <v>0.158993661403656</v>
       </c>
       <c r="N13">
         <v>12.6636277012315</v>
       </c>
       <c r="O13">
-        <v>35.206154999964397</v>
+        <v>35.2061549999644</v>
       </c>
       <c r="P13">
         <v>38.9</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.44590920209884599</v>
+        <v>-0.445909202098846</v>
       </c>
       <c r="C14">
         <v>-0.39159512386959</v>
       </c>
       <c r="D14">
-        <v>16.237859462024598</v>
+        <v>16.2378594620246</v>
       </c>
       <c r="E14">
-        <v>-1.0264204544321001</v>
+        <v>-1.0264204544321</v>
       </c>
       <c r="F14">
-        <v>12949.717486654001</v>
-      </c>
-      <c r="G14" s="2"/>
+        <v>12949.717486654</v>
+      </c>
       <c r="H14">
-        <v>21.182234604866998</v>
+        <v>21.182234604867</v>
       </c>
       <c r="I14">
         <v>14.2886829096862</v>
@@ -1092,7 +1052,6 @@
       <c r="J14">
         <v>10</v>
       </c>
-      <c r="K14" s="2"/>
       <c r="L14">
         <v>-3</v>
       </c>
@@ -1100,7 +1059,7 @@
         <v>0.103040546178818</v>
       </c>
       <c r="N14">
-        <v>12.952841512741299</v>
+        <v>12.9528415127413</v>
       </c>
       <c r="O14">
         <v>30.5265423717108</v>
@@ -1109,7 +1068,7 @@
         <v>40.4</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -1123,12 +1082,11 @@
         <v>14.6171733884386</v>
       </c>
       <c r="E15">
-        <v>2.4053237807943599</v>
+        <v>2.40532378079436</v>
       </c>
       <c r="F15">
         <v>12963.675773326</v>
       </c>
-      <c r="G15" s="2"/>
       <c r="H15">
         <v>21.5652829643596</v>
       </c>
@@ -1138,38 +1096,37 @@
       <c r="J15">
         <v>10.6</v>
       </c>
-      <c r="K15" s="2"/>
       <c r="L15">
         <v>-3.3</v>
       </c>
       <c r="M15">
-        <v>6.5314263105392498E-2</v>
+        <v>0.0653142631053925</v>
       </c>
       <c r="N15">
-        <v>12.452902755807701</v>
+        <v>12.4529027558077</v>
       </c>
       <c r="O15">
-        <v>29.333929002103702</v>
+        <v>29.3339290021037</v>
       </c>
       <c r="P15">
         <v>43.5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>-0.54979139566421498</v>
+        <v>-0.549791395664215</v>
       </c>
       <c r="C16">
         <v>-1.74400211981355</v>
       </c>
       <c r="D16">
-        <v>14.405478589375599</v>
+        <v>14.4054785893756</v>
       </c>
       <c r="E16">
-        <v>-2.5126153208139401</v>
+        <v>-2.51261532081394</v>
       </c>
       <c r="F16">
         <v>12233.1444119186</v>
@@ -1178,39 +1135,39 @@
         <v>24.5697808575806</v>
       </c>
       <c r="H16">
-        <v>22.332294370501401</v>
+        <v>22.3322943705014</v>
       </c>
       <c r="I16">
-        <v>14.001315055851901</v>
+        <v>14.0013150558519</v>
       </c>
       <c r="K16">
-        <v>7.7578891652663904</v>
+        <v>7.75788916526639</v>
       </c>
       <c r="L16">
-        <v>-2.9061460657706499</v>
+        <v>-2.90614606577065</v>
       </c>
       <c r="M16">
-        <v>-5.1218713633716098E-3</v>
+        <v>-0.00512187136337161</v>
       </c>
       <c r="N16">
-        <v>12.610966606719099</v>
+        <v>12.6109666067191</v>
       </c>
       <c r="O16">
-        <v>28.406793645227499</v>
+        <v>28.4067936452275</v>
       </c>
       <c r="P16">
         <v>44.7</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-0.58126527070999101</v>
+        <v>-0.581265270709991</v>
       </c>
       <c r="C17">
-        <v>-2.9629266651353401</v>
+        <v>-2.96292666513534</v>
       </c>
       <c r="D17">
         <v>10.7056520504538</v>
@@ -1222,39 +1179,39 @@
         <v>13679.6264980954</v>
       </c>
       <c r="G17">
-        <v>25.008393234704801</v>
+        <v>25.0083932347048</v>
       </c>
       <c r="H17">
-        <v>22.149080304016401</v>
+        <v>22.1490803040164</v>
       </c>
       <c r="I17">
-        <v>11.780574038525399</v>
+        <v>11.7805740385254</v>
       </c>
       <c r="K17">
-        <v>7.3742107374956101</v>
+        <v>7.37421073749561</v>
       </c>
       <c r="L17">
-        <v>-3.3901103471953502</v>
+        <v>-3.39011034719535</v>
       </c>
       <c r="M17">
-        <v>8.7641347199678404E-3</v>
+        <v>0.00876413471996784</v>
       </c>
       <c r="N17">
         <v>12.3365069418291</v>
       </c>
       <c r="O17">
-        <v>22.486226088979201</v>
+        <v>22.4862260889792</v>
       </c>
       <c r="P17">
         <v>52.6</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>-0.29923555254936202</v>
+        <v>-0.299235552549362</v>
       </c>
       <c r="C18">
         <v>-2.70922168361454</v>
@@ -1263,54 +1220,54 @@
         <v>12.5270951690009</v>
       </c>
       <c r="E18">
-        <v>-2.0803278437781101</v>
+        <v>-2.08032784377811</v>
       </c>
       <c r="F18">
-        <v>12699.962313775601</v>
+        <v>12699.9623137756</v>
       </c>
       <c r="G18">
-        <v>26.179916483246899</v>
+        <v>26.1799164832469</v>
       </c>
       <c r="H18">
-        <v>21.256701307138801</v>
+        <v>21.2567013071388</v>
       </c>
       <c r="I18">
-        <v>13.566792679878899</v>
+        <v>13.5667926798789</v>
       </c>
       <c r="K18">
         <v>11.3900941602608</v>
       </c>
       <c r="L18">
-        <v>-5.3337778270634599</v>
+        <v>-5.33377782706346</v>
       </c>
       <c r="M18">
-        <v>0.19774989783763899</v>
+        <v>0.197749897837639</v>
       </c>
       <c r="N18">
-        <v>12.097283641196199</v>
+        <v>12.0972836411962</v>
       </c>
       <c r="O18">
-        <v>26.093887848879898</v>
+        <v>26.0938878488799</v>
       </c>
       <c r="P18">
         <v>53.1</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>-0.30900245904922502</v>
+        <v>-0.309002459049225</v>
       </c>
       <c r="C19">
-        <v>-4.8399592180739104</v>
+        <v>-4.83995921807391</v>
       </c>
       <c r="D19">
-        <v>11.320283359673301</v>
+        <v>11.3202833596733</v>
       </c>
       <c r="E19">
-        <v>2.8185029777591799</v>
+        <v>2.81850297775918</v>
       </c>
       <c r="F19">
         <v>14532.5009308511</v>
@@ -1319,7 +1276,7 @@
         <v>24.2825320419979</v>
       </c>
       <c r="H19">
-        <v>19.337123974458201</v>
+        <v>19.3371239744582</v>
       </c>
       <c r="I19">
         <v>13.9693177780045</v>
@@ -1328,10 +1285,10 @@
         <v>25.7</v>
       </c>
       <c r="K19">
-        <v>9.4198140180224392</v>
+        <v>9.419814018022439</v>
       </c>
       <c r="L19">
-        <v>-5.5182456950800702</v>
+        <v>-5.51824569508007</v>
       </c>
       <c r="M19">
         <v>0.162542164325714</v>
@@ -1340,54 +1297,54 @@
         <v>10.939623860491</v>
       </c>
       <c r="O19">
-        <v>25.289601137677899</v>
+        <v>25.2896011376779</v>
       </c>
       <c r="P19">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-9.9273927509784698E-2</v>
+        <v>-0.0992739275097847</v>
       </c>
       <c r="C20">
-        <v>-5.1605525715229499</v>
+        <v>-5.16055257152295</v>
       </c>
       <c r="D20">
         <v>14.4366857499034</v>
       </c>
       <c r="E20">
-        <v>-2.6173964628203801</v>
+        <v>-2.61739646282038</v>
       </c>
       <c r="F20">
         <v>11752.7998922979</v>
       </c>
       <c r="G20">
-        <v>22.670943051217101</v>
+        <v>22.6709430512171</v>
       </c>
       <c r="H20">
-        <v>17.702448871729199</v>
+        <v>17.7024488717292</v>
       </c>
       <c r="I20">
         <v>16.3258502050892</v>
       </c>
       <c r="J20">
-        <v>34.277223713100298</v>
+        <v>34.2772237131003</v>
       </c>
       <c r="K20">
         <v>12.8793045637226</v>
       </c>
       <c r="L20">
-        <v>-5.3363522671798798</v>
+        <v>-5.33635226717988</v>
       </c>
       <c r="M20">
-        <v>6.9098123349249398E-3</v>
+        <v>0.00690981233492494</v>
       </c>
       <c r="N20">
-        <v>9.7914471203708899</v>
+        <v>9.79144712037089</v>
       </c>
       <c r="O20">
         <v>30.7625359549926</v>
@@ -1396,7 +1353,7 @@
         <v>85.2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
@@ -1407,34 +1364,34 @@
         <v>-0.779998447561848</v>
       </c>
       <c r="D21">
-        <v>17.924878377846198</v>
+        <v>17.9248783778462</v>
       </c>
       <c r="E21">
         <v>-2.00086100285785</v>
       </c>
       <c r="F21">
-        <v>9955.9747868042796</v>
+        <v>9955.97478680428</v>
       </c>
       <c r="G21">
-        <v>22.036484568694299</v>
+        <v>22.0364845686943</v>
       </c>
       <c r="H21">
-        <v>17.788899050445501</v>
+        <v>17.7888990504455</v>
       </c>
       <c r="I21">
         <v>14.7057366680037</v>
       </c>
       <c r="J21">
-        <v>53.548304349233902</v>
+        <v>53.5483043492339</v>
       </c>
       <c r="K21">
-        <v>15.796798627677701</v>
+        <v>15.7967986276777</v>
       </c>
       <c r="L21">
-        <v>-4.9288970492409598</v>
+        <v>-4.92889704924096</v>
       </c>
       <c r="M21">
-        <v>-9.7823090851306901E-2</v>
+        <v>-0.0978230908513069</v>
       </c>
       <c r="N21">
         <v>10.3919973375121</v>
@@ -1446,7 +1403,7 @@
         <v>89.8</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -1454,40 +1411,40 @@
         <v>-0.163570061326027</v>
       </c>
       <c r="C22">
-        <v>0.69693536113603105</v>
+        <v>0.6969353611360311</v>
       </c>
       <c r="D22">
-        <v>16.605414437248399</v>
+        <v>16.6054144372484</v>
       </c>
       <c r="E22">
-        <v>-9.9004848136464005</v>
+        <v>-9.900484813646401</v>
       </c>
       <c r="F22">
-        <v>8535.5993800438901</v>
+        <v>8535.59938004389</v>
       </c>
       <c r="G22">
         <v>25.8405452538391</v>
       </c>
       <c r="H22">
-        <v>17.477732278309301</v>
+        <v>17.4777322783093</v>
       </c>
       <c r="I22">
         <v>13.5982843701675</v>
       </c>
       <c r="J22">
-        <v>42.015094737650898</v>
+        <v>42.0150947376509</v>
       </c>
       <c r="K22">
-        <v>7.5026430591898698</v>
+        <v>7.50264305918987</v>
       </c>
       <c r="L22">
-        <v>-8.6954919523039003</v>
+        <v>-8.6954919523039</v>
       </c>
       <c r="M22">
-        <v>-7.1997404098510701E-2</v>
+        <v>-0.0719974040985107</v>
       </c>
       <c r="N22">
-        <v>10.708121144490001</v>
+        <v>10.70812114449</v>
       </c>
       <c r="O22">
         <v>30.203698807416</v>
@@ -1496,48 +1453,48 @@
         <v>103.8</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>-0.42259684205055198</v>
+        <v>-0.422596842050552</v>
       </c>
       <c r="C23">
-        <v>1.3615442220344101</v>
+        <v>1.36154422203441</v>
       </c>
       <c r="D23">
         <v>18.0667091690365</v>
       </c>
       <c r="E23">
-        <v>10.441811988250601</v>
+        <v>10.4418119882506</v>
       </c>
       <c r="F23">
         <v>10738.0179223384</v>
       </c>
       <c r="G23">
-        <v>22.896790387781099</v>
+        <v>22.8967903877811</v>
       </c>
       <c r="H23">
-        <v>18.076498904458902</v>
+        <v>18.0764989044589</v>
       </c>
       <c r="I23">
         <v>15.0119803984295</v>
       </c>
       <c r="J23">
-        <v>48.409378625519899</v>
+        <v>48.4093786255199</v>
       </c>
       <c r="K23">
-        <v>6.5236746631393103</v>
+        <v>6.52367466313931</v>
       </c>
       <c r="L23">
         <v>-4.37239542495983</v>
       </c>
       <c r="M23">
-        <v>5.3005863446742296E-4</v>
+        <v>0.000530058634467423</v>
       </c>
       <c r="N23">
-        <v>11.341074033092699</v>
+        <v>11.3410740330927</v>
       </c>
       <c r="O23">
         <v>33.078689567466</v>
@@ -1546,21 +1503,21 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>-0.44722160696983299</v>
+        <v>-0.447221606969833</v>
       </c>
       <c r="C24">
-        <v>-0.62644391921091902</v>
+        <v>-0.626443919210919</v>
       </c>
       <c r="D24">
-        <v>16.248014443902999</v>
+        <v>16.248014443903</v>
       </c>
       <c r="E24">
-        <v>5.2698796738407196</v>
+        <v>5.26987967384072</v>
       </c>
       <c r="F24">
         <v>13935.6811110049</v>
@@ -1578,33 +1535,33 @@
         <v>72.430757531824</v>
       </c>
       <c r="K24">
-        <v>7.7608402884000602</v>
+        <v>7.76084028840006</v>
       </c>
       <c r="L24">
-        <v>-4.4355084756345899</v>
+        <v>-4.43550847563459</v>
       </c>
       <c r="M24">
-        <v>-9.8594330251216902E-2</v>
+        <v>-0.0985943302512169</v>
       </c>
       <c r="N24">
-        <v>11.085818093068699</v>
+        <v>11.0858180930687</v>
       </c>
       <c r="O24">
-        <v>31.547708005107101</v>
+        <v>31.5477080051071</v>
       </c>
       <c r="P24">
         <v>84.3</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>-0.36088395118713401</v>
+        <v>-0.360883951187134</v>
       </c>
       <c r="C25">
-        <v>-3.2118937726638799</v>
+        <v>-3.21189377266388</v>
       </c>
       <c r="D25">
         <v>12.7492457826544</v>
@@ -1613,31 +1570,31 @@
         <v>-1.61100162090189</v>
       </c>
       <c r="F25">
-        <v>14187.482725296501</v>
+        <v>14187.4827252965</v>
       </c>
       <c r="G25">
-        <v>21.118907051075301</v>
+        <v>21.1189070510753</v>
       </c>
       <c r="H25">
-        <v>17.868496972673899</v>
+        <v>17.8684969726739</v>
       </c>
       <c r="I25">
         <v>13.8912663507893</v>
       </c>
       <c r="J25">
-        <v>133.48893559417499</v>
+        <v>133.488935594175</v>
       </c>
       <c r="K25">
-        <v>7.2899441574809796</v>
+        <v>7.28994415748098</v>
       </c>
       <c r="L25">
-        <v>-3.6137162447676201</v>
+        <v>-3.61371624476762</v>
       </c>
       <c r="M25">
-        <v>-0.12751790881156899</v>
+        <v>-0.127517908811569</v>
       </c>
       <c r="N25">
-        <v>9.9809364814131296</v>
+        <v>9.98093648141313</v>
       </c>
       <c r="O25">
         <v>26.6405121334437</v>
@@ -1646,39 +1603,33 @@
         <v>154.6</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>0.90030938364229396</v>
+        <v>0.900309383642294</v>
       </c>
       <c r="D26">
-        <v>15.334233738967599</v>
+        <v>15.3342337389676</v>
       </c>
       <c r="E26">
-        <v>-1.7191051472237699</v>
+        <v>-1.71910514722377</v>
       </c>
       <c r="F26">
         <v>13858.2039802008</v>
       </c>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
       <c r="I26">
-        <v>12.825167695910601</v>
+        <v>12.8251676959106</v>
       </c>
       <c r="J26">
         <v>219.883929014578</v>
       </c>
-      <c r="K26" s="2"/>
       <c r="L26">
         <v>0.5</v>
       </c>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
       <c r="O26">
-        <v>28.159401434878198</v>
+        <v>28.1594014348782</v>
       </c>
       <c r="P26">
         <v>84.7</v>
